--- a/tame_output/ON/bt/strategyON_20240731.xlsx
+++ b/tame_output/ON/bt/strategyON_20240731.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>56.8%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>111.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>450.4%</t>
+          <t>455.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-665.7%</t>
+          <t>-660.5%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-194.8%</t>
+          <t>-192.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-117.7%</t>
+          <t>-104.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-213.8%</t>
+          <t>-205.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-21.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-56.8%</t>
+          <t>-51.7%</t>
         </is>
       </c>
     </row>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082122</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.29349053375792</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803193</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
@@ -47028,10 +47028,10 @@
         <v>1.036928166344344</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3826361916955137</v>
+        <v>0.4151281033338745</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.938399630631198</v>
+        <v>2.957894777614215</v>
       </c>
     </row>
     <row r="1978">
@@ -47051,10 +47051,10 @@
         <v>1.062372215596571</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4302919222565693</v>
+        <v>0.4627838338949302</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.973374825995637</v>
+        <v>2.992869972978653</v>
       </c>
     </row>
     <row r="1979">
@@ -47074,10 +47074,10 @@
         <v>1.107471852370798</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5308100807553239</v>
+        <v>0.5633019923936847</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.038578094469614</v>
+        <v>3.058073241452631</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
@@ -47097,10 +47097,10 @@
         <v>1.069959888685714</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4491117640367902</v>
+        <v>0.4816036756751511</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.976313776914366</v>
+        <v>2.995808923897382</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
@@ -47120,10 +47120,10 @@
         <v>1.091992951939702</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4536551969816597</v>
+        <v>0.4861471086200205</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.983137539291916</v>
+        <v>3.002632686274933</v>
       </c>
     </row>
     <row r="1982">
@@ -47143,10 +47143,10 @@
         <v>1.088354509073977</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4055705557017554</v>
+        <v>0.4380624673401162</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.958447694155052</v>
+        <v>2.977942841138068</v>
       </c>
     </row>
     <row r="1983">
@@ -47166,10 +47166,10 @@
         <v>1.111915246436174</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4497733927876558</v>
+        <v>0.4822653044260167</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.990848998934429</v>
+        <v>3.010344145917446</v>
       </c>
     </row>
     <row r="1984">
@@ -47189,10 +47189,10 @@
         <v>1.095533635840044</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4867472945789864</v>
+        <v>0.5192392062173472</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.011443340478475</v>
+        <v>3.030938487461492</v>
       </c>
     </row>
     <row r="1985">
@@ -47212,10 +47212,10 @@
         <v>1.210097968038793</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4867472945789864</v>
+        <v>0.5192392062173472</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.062691105661515</v>
+        <v>3.082186252644531</v>
       </c>
     </row>
     <row r="1986">
@@ -47235,10 +47235,10 @@
         <v>1.291595474086837</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6943892982134625</v>
+        <v>0.7268812098518234</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.185717012436454</v>
+        <v>3.20521215941947</v>
       </c>
     </row>
     <row r="1987">
@@ -47258,10 +47258,10 @@
         <v>1.306956539414118</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7454213909359905</v>
+        <v>0.7779133025743513</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.21128449630824</v>
+        <v>3.230779643291257</v>
       </c>
     </row>
     <row r="1988">
@@ -47281,10 +47281,10 @@
         <v>1.350233615957705</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8106455720631961</v>
+        <v>0.8431374837015569</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.267606409077268</v>
+        <v>3.287101556060285</v>
       </c>
     </row>
     <row r="1989">
@@ -47304,10 +47304,10 @@
         <v>1.361165396285439</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8158971100923778</v>
+        <v>0.8483890217307386</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.266718304194058</v>
+        <v>3.286213451177074</v>
       </c>
     </row>
     <row r="1990">
@@ -47327,10 +47327,10 @@
         <v>1.354377526202796</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.826924455089797</v>
+        <v>0.8594163667281578</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.27459150352375</v>
+        <v>3.294086650506766</v>
       </c>
     </row>
     <row r="1991">
@@ -47350,10 +47350,10 @@
         <v>1.536433222994889</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8369877645302589</v>
+        <v>0.8694796761686198</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.441187260209237</v>
+        <v>3.460682407192254</v>
       </c>
     </row>
     <row r="1992">
@@ -47373,10 +47373,10 @@
         <v>1.686459036622711</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9117700255552715</v>
+        <v>0.9442619371936324</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.606169526042062</v>
+        <v>3.625664673025079</v>
       </c>
     </row>
     <row r="1993">
@@ -47396,10 +47396,10 @@
         <v>1.688600646342093</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9117700255552715</v>
+        <v>0.9442619371936324</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.597877502055921</v>
+        <v>3.617372649038938</v>
       </c>
     </row>
     <row r="1994">
@@ -47419,10 +47419,10 @@
         <v>1.718046314265451</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9859468364389561</v>
+        <v>1.018438748077317</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.640576784169911</v>
+        <v>3.660071931152928</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
@@ -47442,10 +47442,10 @@
         <v>1.739157704549556</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9859468364389561</v>
+        <v>1.018438748077317</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.658131189896703</v>
+        <v>3.677626336879719</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
@@ -47465,10 +47465,10 @@
         <v>1.663622305166189</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9579990007223753</v>
+        <v>0.9904909123607362</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.633217535871339</v>
+        <v>3.652712682854355</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
@@ -47488,10 +47488,10 @@
         <v>1.924011813898684</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8876509413519647</v>
+        <v>0.9201428529903255</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.572278397436954</v>
+        <v>3.59177354441997</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
@@ -47511,10 +47511,10 @@
         <v>1.92376427786885</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8876509413519647</v>
+        <v>0.9201428529903255</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.562942419933858</v>
+        <v>3.582437566916875</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
@@ -47534,10 +47534,10 @@
         <v>2.030989678402402</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7584491280579224</v>
+        <v>0.7909410396962833</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.644327457808602</v>
+        <v>3.663822604791619</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
@@ -47557,10 +47557,10 @@
         <v>2.006155098184746</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7250814540034463</v>
+        <v>0.7575733656418071</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.661384675869563</v>
+        <v>3.680879822852579</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
@@ -47580,10 +47580,10 @@
         <v>2.00565233026036</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7321361442186201</v>
+        <v>0.7646280558569809</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.662292845988212</v>
+        <v>3.681787992971229</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
@@ -47603,10 +47603,10 @@
         <v>2.026438973635697</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7470164902463392</v>
+        <v>0.7795084018847001</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.681227207249585</v>
+        <v>3.700722354232602</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
@@ -47626,10 +47626,10 @@
         <v>2.15616090255813</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7470164902463392</v>
+        <v>0.7795084018847001</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.865330339394545</v>
+        <v>3.884825486377562</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
@@ -47649,10 +47649,10 @@
         <v>2.139314350339175</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7470164902463392</v>
+        <v>0.7795084018847001</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.857447034297538</v>
+        <v>3.876942181280555</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
@@ -47672,10 +47672,10 @@
         <v>2.082166042897052</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6602894813827977</v>
+        <v>0.6927813930211586</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.807464828529051</v>
+        <v>3.826959975512067</v>
       </c>
     </row>
     <row r="2006">
@@ -47695,10 +47695,10 @@
         <v>2.134643390263487</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7827165989261892</v>
+        <v>0.81520851056455</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.937174816776933</v>
+        <v>3.956669963759949</v>
       </c>
     </row>
     <row r="2007">
@@ -47718,10 +47718,10 @@
         <v>2.116625041874532</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7304429915905479</v>
+        <v>0.7629349032289088</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.908701746920849</v>
+        <v>3.928196893903865</v>
       </c>
     </row>
     <row r="2008">
@@ -47741,10 +47741,10 @@
         <v>2.084204863727945</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7304429915905479</v>
+        <v>0.7629349032289088</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.906813559814624</v>
+        <v>3.926308706797641</v>
       </c>
     </row>
     <row r="2009">
@@ -47764,10 +47764,10 @@
         <v>1.998123605201066</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5281892712661944</v>
+        <v>0.5606811829045553</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.780281557222875</v>
+        <v>3.799776704205891</v>
       </c>
     </row>
     <row r="2010">
@@ -47787,10 +47787,10 @@
         <v>1.931930245200316</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4014063474683151</v>
+        <v>0.4338982591066759</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.702645813154299</v>
+        <v>3.722140960137315</v>
       </c>
     </row>
     <row r="2011">
@@ -47810,10 +47810,10 @@
         <v>1.892083135227213</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4014063474683151</v>
+        <v>0.4338982591066759</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.715719220020218</v>
+        <v>3.735214367003234</v>
       </c>
     </row>
     <row r="2012">
@@ -47833,10 +47833,10 @@
         <v>1.891458478101269</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4014063474683151</v>
+        <v>0.4338982591066759</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.715719220020218</v>
+        <v>3.735214367003234</v>
       </c>
     </row>
     <row r="2013">
@@ -47856,10 +47856,10 @@
         <v>1.878822204384482</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3668094233253802</v>
+        <v>0.3993013349637411</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.693485106661459</v>
+        <v>3.712980253644475</v>
       </c>
     </row>
     <row r="2014">
@@ -47879,10 +47879,10 @@
         <v>1.826576207280523</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2442833206224864</v>
+        <v>0.2767752322608472</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.616733889016921</v>
+        <v>3.636229035999938</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971078</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
@@ -47902,10 +47902,10 @@
         <v>1.801076368396791</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.01376882443689764</v>
+        <v>0.04626073607525849</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.545131150896072</v>
+        <v>3.564626297879088</v>
       </c>
     </row>
     <row r="2016">
@@ -47925,10 +47925,10 @@
         <v>1.838699760200708</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.06215383806855634</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.62039412541163</v>
+        <v>3.639889272394647</v>
       </c>
     </row>
     <row r="2017">
@@ -47948,10 +47948,10 @@
         <v>1.846085462235892</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.06215383806855634</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.68937439455727</v>
+        <v>3.708869541540286</v>
       </c>
     </row>
     <row r="2018">
@@ -47971,10 +47971,10 @@
         <v>1.852345425887079</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.06215383806855634</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.675425596677391</v>
+        <v>3.694920743660407</v>
       </c>
     </row>
     <row r="2019">
@@ -47994,10 +47994,10 @@
         <v>1.763225853339403</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.06215383806855634</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.687296085732805</v>
+        <v>3.706791232715821</v>
       </c>
     </row>
     <row r="2020">
@@ -48017,10 +48017,10 @@
         <v>1.647278085266582</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.06215383806855634</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.688506620251748</v>
+        <v>3.708001767234765</v>
       </c>
     </row>
     <row r="2021">
@@ -48040,10 +48040,10 @@
         <v>1.588382198802127</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1615475548471917</v>
+        <v>-0.1290556432088308</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.652487279394905</v>
+        <v>3.671982426377922</v>
       </c>
     </row>
     <row r="2022">
@@ -48063,10 +48063,10 @@
         <v>1.472274293305007</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2511672891326759</v>
+        <v>-0.2186753774943151</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.593793291559804</v>
+        <v>3.613288438542821</v>
       </c>
     </row>
     <row r="2023">
@@ -48086,10 +48086,10 @@
         <v>1.587691272948495</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2511672891326759</v>
+        <v>-0.2186753774943151</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.755997348258848</v>
+        <v>3.775492495241865</v>
       </c>
     </row>
     <row r="2024">
@@ -48109,10 +48109,10 @@
         <v>1.548650734023928</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.3362833180607223</v>
+        <v>-0.3037914064223615</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.699774368865834</v>
+        <v>3.719269515848851</v>
       </c>
     </row>
     <row r="2025">
@@ -48132,10 +48132,10 @@
         <v>1.526106224284866</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3462180636478025</v>
+        <v>-0.3137261520094417</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.704042939082077</v>
+        <v>3.723538086065094</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717832</v>
+        <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
@@ -48155,10 +48155,10 @@
         <v>1.494241413841405</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4481941858962101</v>
+        <v>-0.4157022742578492</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.651782904188935</v>
+        <v>3.671278051171952</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616949</v>
+        <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
@@ -48178,10 +48178,10 @@
         <v>1.530396814476469</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.4249896139789349</v>
+        <v>-0.392497702340574</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.657858534583476</v>
+        <v>3.677353681566492</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203662</v>
+        <v>3.785578085203661</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
@@ -48201,10 +48201,10 @@
         <v>1.591870655494813</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.4169761873889556</v>
+        <v>-0.3844842757505947</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.666916601259437</v>
+        <v>3.686411748242454</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436928</v>
+        <v>3.777251572436927</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
@@ -48224,10 +48224,10 @@
         <v>1.719710228566084</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.1155294619171183</v>
+        <v>-0.08303755027875748</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.855045519425076</v>
+        <v>3.874540666408092</v>
       </c>
     </row>
     <row r="2030">
@@ -48247,10 +48247,10 @@
         <v>1.710845308624721</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.1155294619171183</v>
+        <v>-0.08303755027875748</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.856016697177786</v>
+        <v>3.875511844160803</v>
       </c>
     </row>
     <row r="2031">
@@ -48270,10 +48270,10 @@
         <v>1.732103563407084</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.1155294619171183</v>
+        <v>-0.08303755027875748</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.856859601557542</v>
+        <v>3.876354748540558</v>
       </c>
     </row>
     <row r="2032">
@@ -48293,10 +48293,10 @@
         <v>1.767597380227882</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.07439016705048751</v>
+        <v>-0.04189825541212666</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.900581277351665</v>
+        <v>3.920076424334682</v>
       </c>
     </row>
     <row r="2033">
@@ -48316,10 +48316,10 @@
         <v>1.628023832383658</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.0362159730291145</v>
+        <v>0.06870788466747535</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.783128957523362</v>
+        <v>3.802624104506378</v>
       </c>
     </row>
     <row r="2034">
@@ -48339,10 +48339,10 @@
         <v>1.579293582645284</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.09436476150172801</v>
+        <v>-0.06187284986336716</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.708282560878819</v>
+        <v>3.727777707861836</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218599</v>
+        <v>3.775043021218598</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
@@ -48362,10 +48362,10 @@
         <v>1.629518935397752</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.09436476150172801</v>
+        <v>-0.06187284986336716</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.692709379954902</v>
+        <v>3.712204526937918</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462768</v>
+        <v>3.821044820462767</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
@@ -48385,10 +48385,10 @@
         <v>1.617758672760409</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.09436476150172801</v>
+        <v>-0.06187284986336716</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.691897090391332</v>
+        <v>3.711392237374348</v>
       </c>
     </row>
     <row r="2037">
@@ -48408,10 +48408,10 @@
         <v>1.623473373929525</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.1047499563916173</v>
+        <v>-0.07225804475325648</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.695534752582471</v>
+        <v>3.715029899565487</v>
       </c>
     </row>
     <row r="2038">
@@ -48431,10 +48431,10 @@
         <v>1.686875116217061</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.1233381151138427</v>
+        <v>-0.09084620347548183</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.755218863125561</v>
+        <v>3.774714010108577</v>
       </c>
     </row>
     <row r="2039">
@@ -48454,10 +48454,10 @@
         <v>1.683624708356945</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.1233381151138427</v>
+        <v>-0.09084620347548183</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.752087873943859</v>
+        <v>3.771583020926875</v>
       </c>
     </row>
     <row r="2040">
@@ -48477,10 +48477,10 @@
         <v>1.728484856772507</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.1108738996294888</v>
+        <v>-0.078381987991128</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.764097298173863</v>
+        <v>3.783592445156879</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.478283254493701</v>
+        <v>3.848510247437698</v>
       </c>
       <c r="C2041" t="n">
         <v>3.830750891430099</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.041179191002573</v>
+        <v>-4.988832586733912</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.813922790715323</v>
+        <v>1.834861432422787</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.1023978015311925</v>
+        <v>0.1872363174382146</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.892189572348815</v>
+        <v>3.943092681893028</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240731.xlsx
+++ b/tame_output/ON/bt/strategyON_20240731.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>19.8%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-80.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.6%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.4%</t>
+          <t>126.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-50.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.2%</t>
+          <t>450.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-660.5%</t>
+          <t>-688.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-192.7%</t>
+          <t>-204.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-104.1%</t>
+          <t>-117.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-205.3%</t>
+          <t>-236.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-51.7%</t>
+          <t>-70.7%</t>
         </is>
       </c>
     </row>
@@ -47028,10 +47028,10 @@
         <v>1.036928166344344</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4151281033338745</v>
+        <v>0.3826361916955137</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.957894777614215</v>
+        <v>2.938399630631198</v>
       </c>
     </row>
     <row r="1978">
@@ -47051,10 +47051,10 @@
         <v>1.062372215596571</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4627838338949302</v>
+        <v>0.4302919222565693</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.992869972978653</v>
+        <v>2.973374825995637</v>
       </c>
     </row>
     <row r="1979">
@@ -47074,10 +47074,10 @@
         <v>1.107471852370798</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5633019923936847</v>
+        <v>0.5308100807553239</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.058073241452631</v>
+        <v>3.038578094469614</v>
       </c>
     </row>
     <row r="1980">
@@ -47097,10 +47097,10 @@
         <v>1.069959888685714</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4816036756751511</v>
+        <v>0.4491117640367902</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.995808923897382</v>
+        <v>2.976313776914366</v>
       </c>
     </row>
     <row r="1981">
@@ -47120,10 +47120,10 @@
         <v>1.091992951939702</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4861471086200205</v>
+        <v>0.4536551969816597</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.002632686274933</v>
+        <v>2.983137539291916</v>
       </c>
     </row>
     <row r="1982">
@@ -47143,10 +47143,10 @@
         <v>1.088354509073977</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4380624673401162</v>
+        <v>0.4055705557017554</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.977942841138068</v>
+        <v>2.958447694155052</v>
       </c>
     </row>
     <row r="1983">
@@ -47166,10 +47166,10 @@
         <v>1.111915246436174</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4822653044260167</v>
+        <v>0.4497733927876558</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.010344145917446</v>
+        <v>2.990848998934429</v>
       </c>
     </row>
     <row r="1984">
@@ -47189,10 +47189,10 @@
         <v>1.095533635840044</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5192392062173472</v>
+        <v>0.4867472945789864</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.030938487461492</v>
+        <v>3.011443340478475</v>
       </c>
     </row>
     <row r="1985">
@@ -47212,10 +47212,10 @@
         <v>1.210097968038793</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5192392062173472</v>
+        <v>0.4867472945789864</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.082186252644531</v>
+        <v>3.062691105661515</v>
       </c>
     </row>
     <row r="1986">
@@ -47235,10 +47235,10 @@
         <v>1.291595474086837</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7268812098518234</v>
+        <v>0.6943892982134625</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.20521215941947</v>
+        <v>3.185717012436454</v>
       </c>
     </row>
     <row r="1987">
@@ -47258,10 +47258,10 @@
         <v>1.306956539414118</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7779133025743513</v>
+        <v>0.7454213909359905</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.230779643291257</v>
+        <v>3.21128449630824</v>
       </c>
     </row>
     <row r="1988">
@@ -47281,10 +47281,10 @@
         <v>1.350233615957705</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8431374837015569</v>
+        <v>0.8106455720631961</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.287101556060285</v>
+        <v>3.267606409077268</v>
       </c>
     </row>
     <row r="1989">
@@ -47304,10 +47304,10 @@
         <v>1.361165396285439</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8483890217307386</v>
+        <v>0.8158971100923778</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.286213451177074</v>
+        <v>3.266718304194058</v>
       </c>
     </row>
     <row r="1990">
@@ -47327,10 +47327,10 @@
         <v>1.354377526202796</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8594163667281578</v>
+        <v>0.826924455089797</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.294086650506766</v>
+        <v>3.27459150352375</v>
       </c>
     </row>
     <row r="1991">
@@ -47350,10 +47350,10 @@
         <v>1.536433222994889</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8694796761686198</v>
+        <v>0.8369877645302589</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.460682407192254</v>
+        <v>3.441187260209237</v>
       </c>
     </row>
     <row r="1992">
@@ -47373,10 +47373,10 @@
         <v>1.686459036622711</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9442619371936324</v>
+        <v>0.9117700255552715</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.625664673025079</v>
+        <v>3.606169526042062</v>
       </c>
     </row>
     <row r="1993">
@@ -47396,10 +47396,10 @@
         <v>1.688600646342093</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9442619371936324</v>
+        <v>0.9117700255552715</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.617372649038938</v>
+        <v>3.597877502055921</v>
       </c>
     </row>
     <row r="1994">
@@ -47419,10 +47419,10 @@
         <v>1.718046314265451</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.018438748077317</v>
+        <v>0.9859468364389561</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.660071931152928</v>
+        <v>3.640576784169911</v>
       </c>
     </row>
     <row r="1995">
@@ -47442,10 +47442,10 @@
         <v>1.739157704549556</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.018438748077317</v>
+        <v>0.9859468364389561</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.677626336879719</v>
+        <v>3.658131189896703</v>
       </c>
     </row>
     <row r="1996">
@@ -47465,10 +47465,10 @@
         <v>1.663622305166189</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9904909123607362</v>
+        <v>0.9579990007223753</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.652712682854355</v>
+        <v>3.633217535871339</v>
       </c>
     </row>
     <row r="1997">
@@ -47488,10 +47488,10 @@
         <v>1.924011813898684</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9201428529903255</v>
+        <v>0.8876509413519647</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.59177354441997</v>
+        <v>3.572278397436954</v>
       </c>
     </row>
     <row r="1998">
@@ -47511,10 +47511,10 @@
         <v>1.92376427786885</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9201428529903255</v>
+        <v>0.8876509413519647</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.582437566916875</v>
+        <v>3.562942419933858</v>
       </c>
     </row>
     <row r="1999">
@@ -47534,10 +47534,10 @@
         <v>2.030989678402402</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7909410396962833</v>
+        <v>0.7584491280579224</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.663822604791619</v>
+        <v>3.644327457808602</v>
       </c>
     </row>
     <row r="2000">
@@ -47557,10 +47557,10 @@
         <v>2.006155098184746</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7575733656418071</v>
+        <v>0.7250814540034463</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.680879822852579</v>
+        <v>3.661384675869563</v>
       </c>
     </row>
     <row r="2001">
@@ -47580,10 +47580,10 @@
         <v>2.00565233026036</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7646280558569809</v>
+        <v>0.7321361442186201</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.681787992971229</v>
+        <v>3.662292845988212</v>
       </c>
     </row>
     <row r="2002">
@@ -47603,10 +47603,10 @@
         <v>2.026438973635697</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7795084018847001</v>
+        <v>0.7470164902463392</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.700722354232602</v>
+        <v>3.681227207249585</v>
       </c>
     </row>
     <row r="2003">
@@ -47626,10 +47626,10 @@
         <v>2.15616090255813</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7795084018847001</v>
+        <v>0.7470164902463392</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.884825486377562</v>
+        <v>3.865330339394545</v>
       </c>
     </row>
     <row r="2004">
@@ -47649,10 +47649,10 @@
         <v>2.139314350339175</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7795084018847001</v>
+        <v>0.7470164902463392</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.876942181280555</v>
+        <v>3.857447034297538</v>
       </c>
     </row>
     <row r="2005">
@@ -47672,10 +47672,10 @@
         <v>2.082166042897052</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6927813930211586</v>
+        <v>0.6602894813827977</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.826959975512067</v>
+        <v>3.807464828529051</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
@@ -47695,10 +47695,10 @@
         <v>2.134643390263487</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.81520851056455</v>
+        <v>0.7827165989261892</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.956669963759949</v>
+        <v>3.937174816776933</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
@@ -47718,10 +47718,10 @@
         <v>2.116625041874532</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7629349032289088</v>
+        <v>0.7304429915905479</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.928196893903865</v>
+        <v>3.908701746920849</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
@@ -47741,10 +47741,10 @@
         <v>2.084204863727945</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7629349032289088</v>
+        <v>0.7304429915905479</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.926308706797641</v>
+        <v>3.906813559814624</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
@@ -47764,10 +47764,10 @@
         <v>1.998123605201066</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5606811829045553</v>
+        <v>0.5281892712661944</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.799776704205891</v>
+        <v>3.780281557222875</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
@@ -47787,10 +47787,10 @@
         <v>1.931930245200316</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4338982591066759</v>
+        <v>0.4014063474683151</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.722140960137315</v>
+        <v>3.702645813154299</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
@@ -47810,10 +47810,10 @@
         <v>1.892083135227213</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4338982591066759</v>
+        <v>0.4014063474683151</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.735214367003234</v>
+        <v>3.715719220020218</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
@@ -47833,10 +47833,10 @@
         <v>1.891458478101269</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4338982591066759</v>
+        <v>0.4014063474683151</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.735214367003234</v>
+        <v>3.715719220020218</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
@@ -47856,10 +47856,10 @@
         <v>1.878822204384482</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3993013349637411</v>
+        <v>0.3668094233253802</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.712980253644475</v>
+        <v>3.693485106661459</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
@@ -47879,10 +47879,10 @@
         <v>1.826576207280523</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2767752322608472</v>
+        <v>0.2442833206224864</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.636229035999938</v>
+        <v>3.616733889016921</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
@@ -47902,10 +47902,10 @@
         <v>1.801076368396791</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.04626073607525849</v>
+        <v>0.01376882443689764</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.564626297879088</v>
+        <v>3.545131150896072</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199803</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
@@ -47925,10 +47925,10 @@
         <v>1.838699760200708</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.06215383806855634</v>
+        <v>-0.09464574970691719</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.639889272394647</v>
+        <v>3.62039412541163</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622233</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
@@ -47948,10 +47948,10 @@
         <v>1.846085462235892</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.06215383806855634</v>
+        <v>-0.09464574970691719</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.708869541540286</v>
+        <v>3.68937439455727</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808525</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
@@ -47971,10 +47971,10 @@
         <v>1.852345425887079</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.06215383806855634</v>
+        <v>-0.09464574970691719</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.694920743660407</v>
+        <v>3.675425596677391</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994891</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
@@ -47994,10 +47994,10 @@
         <v>1.763225853339403</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.06215383806855634</v>
+        <v>-0.09464574970691719</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.706791232715821</v>
+        <v>3.687296085732805</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358295</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
@@ -48017,10 +48017,10 @@
         <v>1.647278085266582</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.06215383806855634</v>
+        <v>-0.09464574970691719</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.708001767234765</v>
+        <v>3.688506620251748</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637086</v>
+        <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
@@ -48040,10 +48040,10 @@
         <v>1.588382198802127</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1290556432088308</v>
+        <v>-0.1615475548471917</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.671982426377922</v>
+        <v>3.652487279394905</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
@@ -48063,10 +48063,10 @@
         <v>1.472274293305007</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2186753774943151</v>
+        <v>-0.2511672891326759</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.613288438542821</v>
+        <v>3.593793291559804</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
@@ -48086,10 +48086,10 @@
         <v>1.587691272948495</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2186753774943151</v>
+        <v>-0.2511672891326759</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.775492495241865</v>
+        <v>3.755997348258848</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>3.696553628456689</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
@@ -48109,10 +48109,10 @@
         <v>1.548650734023928</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.3037914064223615</v>
+        <v>-0.3362833180607223</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.719269515848851</v>
+        <v>3.699774368865834</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253287</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
@@ -48132,10 +48132,10 @@
         <v>1.526106224284866</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3137261520094417</v>
+        <v>-0.3462180636478025</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.723538086065094</v>
+        <v>3.704042939082077</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717831</v>
+        <v>3.78364702771783</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
@@ -48155,10 +48155,10 @@
         <v>1.494241413841405</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4157022742578492</v>
+        <v>-0.4481941858962101</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.671278051171952</v>
+        <v>3.651782904188935</v>
       </c>
     </row>
     <row r="2027">
@@ -48178,10 +48178,10 @@
         <v>1.530396814476469</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.392497702340574</v>
+        <v>-0.4249896139789349</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.677353681566492</v>
+        <v>3.657858534583476</v>
       </c>
     </row>
     <row r="2028">
@@ -48201,10 +48201,10 @@
         <v>1.591870655494813</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.3844842757505947</v>
+        <v>-0.4169761873889556</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.686411748242454</v>
+        <v>3.666916601259437</v>
       </c>
     </row>
     <row r="2029">
@@ -48224,10 +48224,10 @@
         <v>1.719710228566084</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.08303755027875748</v>
+        <v>-0.1155294619171183</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.874540666408092</v>
+        <v>3.855045519425076</v>
       </c>
     </row>
     <row r="2030">
@@ -48247,10 +48247,10 @@
         <v>1.710845308624721</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.08303755027875748</v>
+        <v>-0.1155294619171183</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.875511844160803</v>
+        <v>3.856016697177786</v>
       </c>
     </row>
     <row r="2031">
@@ -48270,10 +48270,10 @@
         <v>1.732103563407084</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.08303755027875748</v>
+        <v>-0.1155294619171183</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.876354748540558</v>
+        <v>3.856859601557542</v>
       </c>
     </row>
     <row r="2032">
@@ -48293,10 +48293,10 @@
         <v>1.767597380227882</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.04189825541212666</v>
+        <v>-0.07439016705048751</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.920076424334682</v>
+        <v>3.900581277351665</v>
       </c>
     </row>
     <row r="2033">
@@ -48316,10 +48316,10 @@
         <v>1.628023832383658</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.06870788466747535</v>
+        <v>0.0362159730291145</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.802624104506378</v>
+        <v>3.783128957523362</v>
       </c>
     </row>
     <row r="2034">
@@ -48339,10 +48339,10 @@
         <v>1.579293582645284</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.06187284986336716</v>
+        <v>-0.09436476150172801</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.727777707861836</v>
+        <v>3.708282560878819</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218598</v>
+        <v>3.775043021218599</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
@@ -48362,10 +48362,10 @@
         <v>1.629518935397752</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.06187284986336716</v>
+        <v>-0.09436476150172801</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.712204526937918</v>
+        <v>3.692709379954902</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462767</v>
+        <v>3.821044820462768</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
@@ -48385,10 +48385,10 @@
         <v>1.617758672760409</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.06187284986336716</v>
+        <v>-0.09436476150172801</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.711392237374348</v>
+        <v>3.691897090391332</v>
       </c>
     </row>
     <row r="2037">
@@ -48408,10 +48408,10 @@
         <v>1.623473373929525</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.07225804475325648</v>
+        <v>-0.1047499563916173</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.715029899565487</v>
+        <v>3.695534752582471</v>
       </c>
     </row>
     <row r="2038">
@@ -48431,10 +48431,10 @@
         <v>1.686875116217061</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.09084620347548183</v>
+        <v>-0.1233381151138427</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.774714010108577</v>
+        <v>3.755218863125561</v>
       </c>
     </row>
     <row r="2039">
@@ -48454,10 +48454,10 @@
         <v>1.683624708356945</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.09084620347548183</v>
+        <v>-0.1233381151138427</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.771583020926875</v>
+        <v>3.752087873943859</v>
       </c>
     </row>
     <row r="2040">
@@ -48477,10 +48477,10 @@
         <v>1.728484856772507</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.078381987991128</v>
+        <v>-0.1108738996294888</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.783592445156879</v>
+        <v>3.764097298173863</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.848510247437698</v>
+        <v>3.478283254493701</v>
       </c>
       <c r="C2041" t="n">
         <v>3.830750891430099</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.988832586733912</v>
+        <v>-5.273106749714053</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.834861432422787</v>
+        <v>1.721151767230731</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.1872363174382146</v>
+        <v>-0.1295297571802884</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.943092681893028</v>
+        <v>3.753033037121926</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240731.xlsx
+++ b/tame_output/ON/bt/strategyON_20240731.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.4%</t>
+          <t>-80.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.1%</t>
+          <t>-50.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>450.0%</t>
+          <t>449.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-688.9%</t>
+          <t>-690.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-204.1%</t>
+          <t>-204.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-117.7%</t>
+          <t>-104.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-236.9%</t>
+          <t>-235.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-21.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-69.9%</t>
         </is>
       </c>
     </row>
@@ -47028,10 +47028,10 @@
         <v>1.036928166344344</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3826361916955137</v>
+        <v>0.4151281033338745</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.938399630631198</v>
+        <v>2.957894777614215</v>
       </c>
     </row>
     <row r="1978">
@@ -47051,10 +47051,10 @@
         <v>1.062372215596571</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4302919222565693</v>
+        <v>0.4627838338949302</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.973374825995637</v>
+        <v>2.992869972978653</v>
       </c>
     </row>
     <row r="1979">
@@ -47074,10 +47074,10 @@
         <v>1.107471852370798</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5308100807553239</v>
+        <v>0.5633019923936847</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.038578094469614</v>
+        <v>3.058073241452631</v>
       </c>
     </row>
     <row r="1980">
@@ -47097,10 +47097,10 @@
         <v>1.069959888685714</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4491117640367902</v>
+        <v>0.4816036756751511</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.976313776914366</v>
+        <v>2.995808923897382</v>
       </c>
     </row>
     <row r="1981">
@@ -47120,10 +47120,10 @@
         <v>1.091992951939702</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4536551969816597</v>
+        <v>0.4861471086200205</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.983137539291916</v>
+        <v>3.002632686274933</v>
       </c>
     </row>
     <row r="1982">
@@ -47143,10 +47143,10 @@
         <v>1.088354509073977</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4055705557017554</v>
+        <v>0.4380624673401162</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.958447694155052</v>
+        <v>2.977942841138068</v>
       </c>
     </row>
     <row r="1983">
@@ -47166,10 +47166,10 @@
         <v>1.111915246436174</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4497733927876558</v>
+        <v>0.4822653044260167</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.990848998934429</v>
+        <v>3.010344145917446</v>
       </c>
     </row>
     <row r="1984">
@@ -47189,10 +47189,10 @@
         <v>1.095533635840044</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4867472945789864</v>
+        <v>0.5192392062173472</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.011443340478475</v>
+        <v>3.030938487461492</v>
       </c>
     </row>
     <row r="1985">
@@ -47212,10 +47212,10 @@
         <v>1.210097968038793</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4867472945789864</v>
+        <v>0.5192392062173472</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.062691105661515</v>
+        <v>3.082186252644531</v>
       </c>
     </row>
     <row r="1986">
@@ -47235,10 +47235,10 @@
         <v>1.291595474086837</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6943892982134625</v>
+        <v>0.7268812098518234</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.185717012436454</v>
+        <v>3.20521215941947</v>
       </c>
     </row>
     <row r="1987">
@@ -47258,10 +47258,10 @@
         <v>1.306956539414118</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7454213909359905</v>
+        <v>0.7779133025743513</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.21128449630824</v>
+        <v>3.230779643291257</v>
       </c>
     </row>
     <row r="1988">
@@ -47281,10 +47281,10 @@
         <v>1.350233615957705</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8106455720631961</v>
+        <v>0.8431374837015569</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.267606409077268</v>
+        <v>3.287101556060285</v>
       </c>
     </row>
     <row r="1989">
@@ -47304,10 +47304,10 @@
         <v>1.361165396285439</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8158971100923778</v>
+        <v>0.8483890217307386</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.266718304194058</v>
+        <v>3.286213451177074</v>
       </c>
     </row>
     <row r="1990">
@@ -47327,10 +47327,10 @@
         <v>1.354377526202796</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.826924455089797</v>
+        <v>0.8594163667281578</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.27459150352375</v>
+        <v>3.294086650506766</v>
       </c>
     </row>
     <row r="1991">
@@ -47350,10 +47350,10 @@
         <v>1.536433222994889</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8369877645302589</v>
+        <v>0.8694796761686198</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.441187260209237</v>
+        <v>3.460682407192254</v>
       </c>
     </row>
     <row r="1992">
@@ -47373,10 +47373,10 @@
         <v>1.686459036622711</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9117700255552715</v>
+        <v>0.9442619371936324</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.606169526042062</v>
+        <v>3.625664673025079</v>
       </c>
     </row>
     <row r="1993">
@@ -47396,10 +47396,10 @@
         <v>1.688600646342093</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9117700255552715</v>
+        <v>0.9442619371936324</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.597877502055921</v>
+        <v>3.617372649038938</v>
       </c>
     </row>
     <row r="1994">
@@ -47419,10 +47419,10 @@
         <v>1.718046314265451</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9859468364389561</v>
+        <v>1.018438748077317</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.640576784169911</v>
+        <v>3.660071931152928</v>
       </c>
     </row>
     <row r="1995">
@@ -47442,10 +47442,10 @@
         <v>1.739157704549556</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9859468364389561</v>
+        <v>1.018438748077317</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.658131189896703</v>
+        <v>3.677626336879719</v>
       </c>
     </row>
     <row r="1996">
@@ -47465,10 +47465,10 @@
         <v>1.663622305166189</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9579990007223753</v>
+        <v>0.9904909123607362</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.633217535871339</v>
+        <v>3.652712682854355</v>
       </c>
     </row>
     <row r="1997">
@@ -47488,10 +47488,10 @@
         <v>1.924011813898684</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8876509413519647</v>
+        <v>0.9201428529903255</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.572278397436954</v>
+        <v>3.59177354441997</v>
       </c>
     </row>
     <row r="1998">
@@ -47511,10 +47511,10 @@
         <v>1.92376427786885</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8876509413519647</v>
+        <v>0.9201428529903255</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.562942419933858</v>
+        <v>3.582437566916875</v>
       </c>
     </row>
     <row r="1999">
@@ -47534,10 +47534,10 @@
         <v>2.030989678402402</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7584491280579224</v>
+        <v>0.7909410396962833</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.644327457808602</v>
+        <v>3.663822604791619</v>
       </c>
     </row>
     <row r="2000">
@@ -47557,10 +47557,10 @@
         <v>2.006155098184746</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7250814540034463</v>
+        <v>0.7575733656418071</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.661384675869563</v>
+        <v>3.680879822852579</v>
       </c>
     </row>
     <row r="2001">
@@ -47580,10 +47580,10 @@
         <v>2.00565233026036</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7321361442186201</v>
+        <v>0.7646280558569809</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.662292845988212</v>
+        <v>3.681787992971229</v>
       </c>
     </row>
     <row r="2002">
@@ -47603,10 +47603,10 @@
         <v>2.026438973635697</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7470164902463392</v>
+        <v>0.7795084018847001</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.681227207249585</v>
+        <v>3.700722354232602</v>
       </c>
     </row>
     <row r="2003">
@@ -47626,10 +47626,10 @@
         <v>2.15616090255813</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7470164902463392</v>
+        <v>0.7795084018847001</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.865330339394545</v>
+        <v>3.884825486377562</v>
       </c>
     </row>
     <row r="2004">
@@ -47649,10 +47649,10 @@
         <v>2.139314350339175</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7470164902463392</v>
+        <v>0.7795084018847001</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.857447034297538</v>
+        <v>3.876942181280555</v>
       </c>
     </row>
     <row r="2005">
@@ -47672,10 +47672,10 @@
         <v>2.082166042897052</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6602894813827977</v>
+        <v>0.6927813930211586</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.807464828529051</v>
+        <v>3.826959975512067</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
@@ -47695,10 +47695,10 @@
         <v>2.134643390263487</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7827165989261892</v>
+        <v>0.81520851056455</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.937174816776933</v>
+        <v>3.956669963759949</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
@@ -47718,10 +47718,10 @@
         <v>2.116625041874532</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7304429915905479</v>
+        <v>0.7629349032289088</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.908701746920849</v>
+        <v>3.928196893903865</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
@@ -47741,10 +47741,10 @@
         <v>2.084204863727945</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7304429915905479</v>
+        <v>0.7629349032289088</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.906813559814624</v>
+        <v>3.926308706797641</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
@@ -47764,10 +47764,10 @@
         <v>1.998123605201066</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5281892712661944</v>
+        <v>0.5606811829045553</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.780281557222875</v>
+        <v>3.799776704205891</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
@@ -47787,10 +47787,10 @@
         <v>1.931930245200316</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4014063474683151</v>
+        <v>0.4338982591066759</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.702645813154299</v>
+        <v>3.722140960137315</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
@@ -47810,10 +47810,10 @@
         <v>1.892083135227213</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4014063474683151</v>
+        <v>0.4338982591066759</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.715719220020218</v>
+        <v>3.735214367003234</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
@@ -47833,10 +47833,10 @@
         <v>1.891458478101269</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4014063474683151</v>
+        <v>0.4338982591066759</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.715719220020218</v>
+        <v>3.735214367003234</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
@@ -47856,10 +47856,10 @@
         <v>1.878822204384482</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3668094233253802</v>
+        <v>0.3993013349637411</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.693485106661459</v>
+        <v>3.712980253644475</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
@@ -47879,10 +47879,10 @@
         <v>1.826576207280523</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2442833206224864</v>
+        <v>0.2767752322608472</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.616733889016921</v>
+        <v>3.636229035999938</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
@@ -47902,10 +47902,10 @@
         <v>1.801076368396791</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.01376882443689764</v>
+        <v>0.04626073607525849</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.545131150896072</v>
+        <v>3.564626297879088</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199803</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
@@ -47925,10 +47925,10 @@
         <v>1.838699760200708</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.06215383806855634</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.62039412541163</v>
+        <v>3.639889272394647</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622233</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
@@ -47948,10 +47948,10 @@
         <v>1.846085462235892</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.06215383806855634</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.68937439455727</v>
+        <v>3.708869541540286</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808525</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
@@ -47971,10 +47971,10 @@
         <v>1.852345425887079</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.06215383806855634</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.675425596677391</v>
+        <v>3.694920743660407</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994891</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
@@ -47994,10 +47994,10 @@
         <v>1.763225853339403</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.06215383806855634</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.687296085732805</v>
+        <v>3.706791232715821</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358295</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
@@ -48017,10 +48017,10 @@
         <v>1.647278085266582</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.06215383806855634</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.688506620251748</v>
+        <v>3.708001767234765</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
@@ -48040,10 +48040,10 @@
         <v>1.588382198802127</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1615475548471917</v>
+        <v>-0.1290556432088308</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.652487279394905</v>
+        <v>3.671982426377922</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
@@ -48063,10 +48063,10 @@
         <v>1.472274293305007</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2511672891326759</v>
+        <v>-0.2186753774943151</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.593793291559804</v>
+        <v>3.613288438542821</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
@@ -48086,10 +48086,10 @@
         <v>1.587691272948495</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2511672891326759</v>
+        <v>-0.2186753774943151</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.755997348258848</v>
+        <v>3.775492495241865</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456689</v>
+        <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
@@ -48109,10 +48109,10 @@
         <v>1.548650734023928</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.3362833180607223</v>
+        <v>-0.3037914064223615</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.699774368865834</v>
+        <v>3.719269515848851</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253287</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
@@ -48132,10 +48132,10 @@
         <v>1.526106224284866</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3462180636478025</v>
+        <v>-0.3137261520094417</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.704042939082077</v>
+        <v>3.723538086065094</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78364702771783</v>
+        <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
@@ -48155,10 +48155,10 @@
         <v>1.494241413841405</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4481941858962101</v>
+        <v>-0.4157022742578492</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.651782904188935</v>
+        <v>3.671278051171952</v>
       </c>
     </row>
     <row r="2027">
@@ -48178,10 +48178,10 @@
         <v>1.530396814476469</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.4249896139789349</v>
+        <v>-0.392497702340574</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.657858534583476</v>
+        <v>3.677353681566492</v>
       </c>
     </row>
     <row r="2028">
@@ -48201,10 +48201,10 @@
         <v>1.591870655494813</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.4169761873889556</v>
+        <v>-0.3844842757505947</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.666916601259437</v>
+        <v>3.686411748242454</v>
       </c>
     </row>
     <row r="2029">
@@ -48224,10 +48224,10 @@
         <v>1.719710228566084</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.1155294619171183</v>
+        <v>-0.08303755027875748</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.855045519425076</v>
+        <v>3.874540666408092</v>
       </c>
     </row>
     <row r="2030">
@@ -48247,10 +48247,10 @@
         <v>1.710845308624721</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.1155294619171183</v>
+        <v>-0.08303755027875748</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.856016697177786</v>
+        <v>3.875511844160803</v>
       </c>
     </row>
     <row r="2031">
@@ -48270,10 +48270,10 @@
         <v>1.732103563407084</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.1155294619171183</v>
+        <v>-0.08303755027875748</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.856859601557542</v>
+        <v>3.876354748540558</v>
       </c>
     </row>
     <row r="2032">
@@ -48293,10 +48293,10 @@
         <v>1.767597380227882</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.07439016705048751</v>
+        <v>-0.04189825541212666</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.900581277351665</v>
+        <v>3.920076424334682</v>
       </c>
     </row>
     <row r="2033">
@@ -48316,10 +48316,10 @@
         <v>1.628023832383658</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.0362159730291145</v>
+        <v>0.06870788466747535</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.783128957523362</v>
+        <v>3.802624104506378</v>
       </c>
     </row>
     <row r="2034">
@@ -48339,10 +48339,10 @@
         <v>1.579293582645284</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.09436476150172801</v>
+        <v>-0.06187284986336716</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.708282560878819</v>
+        <v>3.727777707861836</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218599</v>
+        <v>3.775043021218598</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
@@ -48362,10 +48362,10 @@
         <v>1.629518935397752</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.09436476150172801</v>
+        <v>-0.06187284986336716</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.692709379954902</v>
+        <v>3.712204526937918</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462768</v>
+        <v>3.821044820462767</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
@@ -48385,10 +48385,10 @@
         <v>1.617758672760409</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.09436476150172801</v>
+        <v>-0.06187284986336716</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.691897090391332</v>
+        <v>3.711392237374348</v>
       </c>
     </row>
     <row r="2037">
@@ -48408,10 +48408,10 @@
         <v>1.623473373929525</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.1047499563916173</v>
+        <v>-0.07225804475325648</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.695534752582471</v>
+        <v>3.715029899565487</v>
       </c>
     </row>
     <row r="2038">
@@ -48431,10 +48431,10 @@
         <v>1.686875116217061</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.1233381151138427</v>
+        <v>-0.09084620347548183</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.755218863125561</v>
+        <v>3.774714010108577</v>
       </c>
     </row>
     <row r="2039">
@@ -48454,10 +48454,10 @@
         <v>1.683624708356945</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.1233381151138427</v>
+        <v>-0.09084620347548183</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.752087873943859</v>
+        <v>3.771583020926875</v>
       </c>
     </row>
     <row r="2040">
@@ -48477,10 +48477,10 @@
         <v>1.728484856772507</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.1108738996294888</v>
+        <v>-0.078381987991128</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.764097298173863</v>
+        <v>3.783592445156879</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.830750891430099</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.273106749714053</v>
+        <v>-5.29225475873455</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.721151767230731</v>
+        <v>1.713492563622532</v>
       </c>
       <c r="F2041" t="n">
-        <v>-0.1295297571802884</v>
+        <v>-0.1161858545624236</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.753033037121926</v>
+        <v>3.761039378692645</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240731.xlsx
+++ b/tame_output/ON/bt/strategyON_20240731.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>342</v>
+        <v>441</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>111.6%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,55 +791,55 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>5.4%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,17 +949,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.3%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -969,35 +969,35 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-640.0%</t>
+          <t>-106.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,32 +1007,32 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.9%</t>
+          <t>439.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-690.8%</t>
+          <t>-64.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1127,35 +1127,35 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-256.4%</t>
+          <t>-40.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-153.8%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-204.9%</t>
+          <t>-20.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1285,20 +1285,20 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-262.8%</t>
+          <t>-57.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,32 +1323,32 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-104.1%</t>
+          <t>-149.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-235.6%</t>
+          <t>-25.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>106.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,20 +1443,20 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.1%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>105.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-69.9%</t>
+          <t>-9.8%</t>
         </is>
       </c>
     </row>
@@ -43773,22 +43773,22 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1836" t="n">
-        <v>3.118001050765402</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.3997263829116132</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.2775351796163</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1836" t="n">
         <v>1.668418790368211</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.119052324986328</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1837" t="n">
-        <v>3.118490189491276</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.3243370297764078</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.247868577088092</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1837" t="n">
         <v>1.668418790368211</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.119541463712203</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1838" t="n">
-        <v>3.122570172112943</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1878921395489951</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.197370603618793</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.531973900140798</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.041754512197421</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1839" t="n">
-        <v>3.157511256610484</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.04923935230080001</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.137459091376417</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.531973900140798</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.076695596694964</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1840" t="n">
-        <v>3.156088696795822</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.04420176157321348</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.13805156785279</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.587618356407115</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.108659710640092</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1841" t="n">
-        <v>3.13483507841956</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.3013957962812702</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.013920335593304</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.330424321699059</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.933089671438995</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1842" t="n">
-        <v>3.13585268755003</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3671631863306823</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.988630988704009</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.330424321699059</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.934107280569465</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1843" t="n">
-        <v>3.126480719537785</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5724078633879268</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.897161149868867</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.330424321699059</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.924735312557221</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1844" t="n">
-        <v>3.116563445493024</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6541797638156785</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.854535115653005</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.357459895105195</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.931039382556141</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1845" t="n">
-        <v>3.121328762326726</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7213888716875563</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.832416789337956</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.357459895105195</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.935804699389843</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1846" t="n">
-        <v>3.119153558445966</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7099996350327549</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.834797280119117</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.368849131759997</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.940463037501964</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1847" t="n">
-        <v>3.117080449951029</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.127753658579592</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.665622562205445</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9510951082131597</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.687737514878926</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1848" t="n">
-        <v>3.116946666549951</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.417885325185023</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.549436112162195</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.9751769029533396</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.702052808321955</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1849" t="n">
-        <v>3.121838811103876</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.625889383538101</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.471126633374889</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.9751769029533396</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.70694495287588</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1850" t="n">
-        <v>3.116920267441865</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.688067794699071</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.441336725248489</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9129984917923695</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.664719362517286</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1851" t="n">
-        <v>3.110004566748314</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.054136521843724</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.287993533697077</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5469297646477168</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.438162425536944</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1852" t="n">
-        <v>3.130342856487082</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.262627303295408</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.224935510855171</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3384389831960324</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.333406246404702</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1853" t="n">
-        <v>3.13844160689565</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.50982848806063</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.134153787357651</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3585923366948448</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.353597008912558</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1854" t="n">
-        <v>3.139547998939383</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.002213516084727</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.938306168191745</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1337926913292519</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.059272384141832</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1855" t="n">
-        <v>3.138090537752246</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.387393907014799</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.782776550632579</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1337926913292519</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.057814922954695</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.139859661206862</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.637264587029381</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.684597402081363</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.09752997149878867</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.081341678307589</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.13596571986312</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.843776363916402</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.598098749982812</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3040417483858102</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.953540670831634</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.137738646563379</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.163120438996904</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.472134046650871</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3040417483858102</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.955313597531894</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.124071534030784</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.549330270272679</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.303983001607965</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.3948146881032535</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.887182721168832</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.112356309032875</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.784024264405232</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.198390178957035</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3884784208739983</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.879269256508476</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.11093690068884</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.119686911635684</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.062705711720819</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4564094063629031</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.837091256871098</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.117424460923081</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.196131241838556</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.038615539873912</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3759638972692412</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.891846122561537</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.116678975928913</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.561258624477302</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8918191018242445</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6722746815682538</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.713314166987961</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.115440519943672</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.969847401657981</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7271451349667317</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.080863458748932</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.466922444694313</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.110625952415132</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.083607813680846</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6768264026290467</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.080863458748932</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.462107877165773</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.10862000302401</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.499999687967843</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.508263703523125</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.080863458748932</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.460101927774651</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.118878693692689</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.861173317784831</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.374052942265009</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.080863458748932</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.47036061844333</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.114978258838384</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.20443183742785</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2328490995534964</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.080863458748932</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.466460183589025</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.113383178893385</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.252634654670194</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2119728927115596</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.080863458748932</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.464865103644026</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.117162154822593</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.549295996480391</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.09708733191668895</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.149606594482811</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.427398198132907</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.11313585028819</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.736015704789694</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.01837314405856461</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.149606594482811</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.423371893598504</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.113033748966606</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.119017093532324</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.1349295127600714</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.149606594482811</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.42326979227692</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.115605264938036</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.123503538733713</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1341525748691965</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.154093039684199</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.423149441127517</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.120955568236086</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.483033861237715</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2726144005727473</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.154093039684199</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.428499744425567</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.128871588193264</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.533382924691937</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2848380059972584</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.204442103138421</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.406206326310211</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.825905229988204</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.131913338815032</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.631002202113333</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3208439663440479</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.302061380559818</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.350676510479142</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.604631100061017</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.134806895136605</v>
+        <v>3.138175778137954</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.685073701621691</v>
+        <v>0.5569366923534892</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3395790098258193</v>
+        <v>3.360594030765603</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.356132880068178</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.321127167095698</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.61497278726522</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.140320092255247</v>
+        <v>3.143688975256597</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.889331876951555</v>
+        <v>0.3526785170236256</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4157690828391223</v>
+        <v>3.2844039577523</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.483771824682167</v>
+        <v>1.540779845754222</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.250056997445947</v>
+        <v>4.06815688270913</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.609034292853409</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.144802646739683</v>
+        <v>3.148171529741033</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.922984715460029</v>
+        <v>0.3190256785151517</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4247476637580756</v>
+        <v>3.275425376833346</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.584185192599204</v>
+        <v>1.440366477837185</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.194291531180161</v>
+        <v>4.012391416443344</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.160174348233104</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.84951488379258</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.379988029597675</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.510715360931755</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.253745131674051</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.174729568980621</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.024639301179123</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4354825758047758</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.685839778318299</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.163225701989642</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.167510404079025</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.259091395193613</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5364825783121674</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.685839778318299</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.156006537088046</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.160838213305049</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.363466126220059</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5849046614967222</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.790214509344745</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.086709507698202</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.161954003143605</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.416252281820386</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6049033338982968</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.885889995927142</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.03042000558732</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.16464773177272</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.542289075188675</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6526243226164978</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.8606383731174</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.04826470790228</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.168638067459121</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.485217303292744</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6258052781717245</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.8606383731174</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.052255043588681</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.167162840560379</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.626889145016865</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6839492417601143</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.8606383731174</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.050779816689939</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.182216250725251</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.57729830059203</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6490594938253085</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.811047528692566</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.095587733509712</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.169165117078568</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.428379966120174</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6025432936832487</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.779797937957393</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.101286354304133</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.178744190114777</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.202534813400764</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5026261595592758</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.737871262370229</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.136021432692639</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.179883334670836</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.077956157063172</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4516555524681802</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.737871262370229</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.137160577248698</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.182517108832943</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.130851445107458</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4701798935237873</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.732915916281783</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.142767559063874</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.18825081307158</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.058718269819577</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4355929191699985</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.732915916281783</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14850126330251</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.178513550677715</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.98735187720993</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4167836245200047</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.661549523672135</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.181583836474434</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.168630069364807</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.893892843224705</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3892834922388224</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.661549523672135</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.171700355161526</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.166795508865433</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.883239661671274</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3868567801168235</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.661549523672135</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.169865794662153</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.166495193891973</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.785332622994783</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3479942796196882</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.593563773811579</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.210356929605025</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.167163700037466</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.761379082018825</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3377443570838112</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.569610232835621</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.225397560336094</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.153903383875714</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.497319143696028</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2453806979164446</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.305550294512825</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.370573207168019</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.151116350215413</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.79023952019119</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.03466411782518986</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.305550294512825</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.367786173507719</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.151459974103255</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.750055221825</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.05108146105950739</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.265365996146634</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.392240376415274</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.461454158459341</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.150826795324011</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.586655350885637</v>
+        <v>0.3871567198501421</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1158082306560093</v>
+        <v>3.318049494860764</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.101966125207272</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.489647120199649</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>4.006902670095509</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.158751224161864</v>
+        <v>3.163543231234454</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.353174128656039</v>
+        <v>0.3984231136234098</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2171251483857009</v>
+        <v>3.322556052370071</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8684849029776731</v>
+        <v>1.508497519172175</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.63766028237526</v>
+        <v>4.068641742737759</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>4.021209363589485</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.160651020921495</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.203507737648524</v>
+        <v>0.5480895046309247</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.274099494475748</v>
+        <v>3.379530398460117</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7755814117351372</v>
+        <v>1.601401010414711</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.690510166807822</v>
+        <v>4.121491627170322</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.769398491143837</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.156018507668522</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.071232264017637</v>
+        <v>0.7007501855493687</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3223771706751295</v>
+        <v>3.435962157574522</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6433059381042505</v>
+        <v>1.754061691333155</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.765242937733382</v>
+        <v>4.208455522468415</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.769398491143837</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.156018507668522</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.915493931457895</v>
+        <v>0.7007501855493687</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3874875643866629</v>
+        <v>3.435962157574522</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.487567605544509</v>
+        <v>1.754061691333155</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.861500997956863</v>
+        <v>4.208455522468415</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.769398491143837</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.156018507668522</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.666494132774314</v>
+        <v>0.7007501855493687</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4999938250837541</v>
+        <v>3.435962157574522</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2385678068609283</v>
+        <v>1.754061691333155</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.023807218390671</v>
+        <v>4.208455522468415</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.769398491143837</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>3.156018507668522</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.772084122547419</v>
+        <v>0.7007501855493687</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3297818995752935</v>
+        <v>3.435962157574522</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3441577966340326</v>
+        <v>1.754061691333155</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.832477294927589</v>
+        <v>4.208455522468415</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.769398491143837</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>3.156018507668522</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.790819024666016</v>
+        <v>0.7007501855493687</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3708322806049411</v>
+        <v>3.435962157574522</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3497538062941639</v>
+        <v>1.754061691333155</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.877664031008597</v>
+        <v>4.208455522468415</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>4.043803538856293</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>3.156018507668522</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.642878983258417</v>
+        <v>0.7111039312128948</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3101293744798133</v>
+        <v>3.440103655839933</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3294328903856064</v>
+        <v>1.754061691333155</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.769977657865564</v>
+        <v>4.208455522468415</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>4.007036081554686</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>3.147304521415044</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.589909461004428</v>
+        <v>0.7640734534668837</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3226031971279304</v>
+        <v>3.45257747848805</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2764633681316175</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.793045384964479</v>
+        <v>4.231523249567331</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.546361054233738</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3330619477411134</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2764633681316175</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.786084772869386</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.512997847754969</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3608695847137642</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2764633681316175</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.800547127250529</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.404738710632447</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3987053600219679</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2764633681316175</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.795079247709724</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.281447575815316</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.445519907959397</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.153172233314487</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.866552022610579</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.260298376911873</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4616805657580993</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1320230344110436</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.88694252018997</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.016532934928429</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5549674508985278</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1320230344110436</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.882723228537021</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.914770114651134</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5977968929294621</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1188039660186149</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.892778983492494</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.664919720702059</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6904791254927938</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1188039660186149</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.885521058476196</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.489027628234627</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7644350860004154</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1188039660186149</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.889120181996845</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.317581165212164</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8463411772639544</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.05264249700384821</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.005315565864877</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.243291599473825</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.875077481175587</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1269320627421875</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.048909782924177</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.17965585723989</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9052265791234784</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.190567804976122</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.091786029318855</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.06822909791397</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.930991541637642</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.190567804976122</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.072980288102651</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.078731720979259</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9285335690364036</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1800651819108331</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.068421790888355</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.006489152808064</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9613599101397019</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1800651819108331</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.072351104723175</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.988775465930199</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9691239688081881</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.18324651080775</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.074938485978665</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.879970580450472</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.009643994220072</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.18324651080775</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.071936557198658</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.659949782413461</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.099231350445491</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3244663558757302</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.158247501250061</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>4.063112455146479</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.527082093350184</v>
+        <v>0.8116145259984449</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.168272608872625</v>
+        <v>3.464633295405581</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3244663558757302</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.174141684051884</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>4.12058087848802</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>3.140343909319951</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.406909009985685</v>
+        <v>0.8055875014683731</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.217487686658726</v>
+        <v>3.462222485593553</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4446394392402291</v>
+        <v>1.807031213587144</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.247391378510885</v>
+        <v>4.224562637472237</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.742626499572066</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>3.15043201188139</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.262236864885947</v>
+        <v>0.9391451149986102</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.285444647260061</v>
+        <v>3.525733633567087</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5893115843399666</v>
+        <v>1.940588827117381</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.344282768132168</v>
+        <v>4.314785308151819</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.742626499572066</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>3.15043201188139</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.32211169224364</v>
+        <v>0.9391451149986102</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.24753220771841</v>
+        <v>3.525733633567087</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5294367569822744</v>
+        <v>1.940588827117381</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.294395363118978</v>
+        <v>4.314785308151819</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.742626499572066</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.992022478163822</v>
+        <v>3.15043201188139</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.202291461332803</v>
+        <v>0.9391451149986102</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.310749469316953</v>
+        <v>3.525733633567087</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5294367569822744</v>
+        <v>1.940588827117381</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.309684532353187</v>
+        <v>4.314785308151819</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.742626499572066</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.899666677486263</v>
+        <v>3.15043201188139</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.204761167794609</v>
+        <v>0.9391451149986102</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.217405786054673</v>
+        <v>3.525733633567087</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5269670505204682</v>
+        <v>1.940588827117381</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.215846907798545</v>
+        <v>4.314785308151819</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.742626499572066</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.818928538971565</v>
+        <v>3.15043201188139</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.273131354118619</v>
+        <v>0.9391451149986102</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.10931957301037</v>
+        <v>3.525733633567087</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5362427495566832</v>
+        <v>1.940588827117381</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.140674188705575</v>
+        <v>4.314785308151819</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.742626499572066</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.809365247603456</v>
+        <v>3.15043201188139</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.286919406965666</v>
+        <v>0.9391451149986102</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.094241060503442</v>
+        <v>3.525733633567087</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5362427495566832</v>
+        <v>1.940588827117381</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.131110897337466</v>
+        <v>4.314785308151819</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.742626499572066</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.946396084295658</v>
+        <v>3.15043201188139</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.342439482858255</v>
+        <v>0.9391451149986102</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.209063866838609</v>
+        <v>3.525733633567087</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5362427495566832</v>
+        <v>1.940588827117381</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.268141734029669</v>
+        <v>4.314785308151819</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.742626499572066</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.950963316287446</v>
+        <v>3.15043201188139</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.166965223065786</v>
+        <v>0.9391451149986102</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.283820802747385</v>
+        <v>3.525733633567087</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5362427495566832</v>
+        <v>1.940588827117381</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.272708966021456</v>
+        <v>4.314785308151819</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.742626499572066</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.926705345048653</v>
+        <v>3.15043201188139</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.277901475707035</v>
+        <v>0.9391451149986102</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.215188330452092</v>
+        <v>3.525733633567087</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5362427495566832</v>
+        <v>1.940588827117381</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.248450994782663</v>
+        <v>4.314785308151819</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>4.230777191174315</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.855243658450103</v>
+        <v>3.15043201188139</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.244237930234752</v>
+        <v>0.9407975304777006</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.157192062042455</v>
+        <v>3.526394599758723</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5699062950289651</v>
+        <v>1.940588827117381</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.197187435467483</v>
+        <v>4.314785308151819</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>4.241910846327185</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.865416044882235</v>
+        <v>3.160604398313523</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.184385311031029</v>
+        <v>1.000650149681424</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.191305496156077</v>
+        <v>3.560508033872345</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5699062950289651</v>
+        <v>1.940588827117381</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.207359821899615</v>
+        <v>4.324957694583952</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>4.244516851805321</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.860362315456096</v>
+        <v>3.155550668887383</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.098141848004651</v>
+        <v>1.086893612707801</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.220749151940488</v>
+        <v>3.589951689656756</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5699062950289651</v>
+        <v>1.940588827117381</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.202306092473475</v>
+        <v>4.319903965157811</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>4.209594393379068</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.852138090900621</v>
+        <v>3.147326444331909</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.143448667403631</v>
+        <v>1.041586793308821</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.194402199625421</v>
+        <v>3.56360473734169</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5290961320197343</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.169595770112462</v>
+        <v>4.287193642796799</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.852689963933723</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.172481772105932</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.183340830777603</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5290961320197343</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.170147643145564</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.781962655825089</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.079671290655073</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.149737715249312</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6219066134705936</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.155106623907445</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.783836131749689</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.1240607599845</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.133855403442142</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.577517144141166</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.130346418234389</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.778911840261412</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.240602365089843</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.082314469911728</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4609755390358232</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.055497163682907</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.78440313609208</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.12822536390717</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.132756566215464</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4609755390358232</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.060988459513574</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.795900337860619</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.156005761808522</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.133141608823462</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4331951411344701</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.055817422541301</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.634256057861272</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.274386434538661</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9241450597320604</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3659772889834939</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.853842431251369</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.754405718580478</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.383000512981992</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.000849089073933</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3659772889834939</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.973992091970574</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.768918744682801</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.347591474733849</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.029525730475514</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3659772889834939</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.988505118072897</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.766338186025169</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.309207812175698</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.042298636841143</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4043609515416451</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.008954756950156</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.763067214870471</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.132091482140532</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.109874197700511</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4043609515416451</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.005683785795458</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.763750606632384</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.177183726974078</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.092520691529006</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3424649083722553</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.969229551655738</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.757537581938799</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.99780830573531</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.158057835330927</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.499241666542974</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.057082581864583</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.738345037270388</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.042822519255916</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.120859605254275</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4688927712283694</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.01968070000741</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>4.273630651107124</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.744036599609334</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.309827029528351</v>
+        <v>1.012257448289408</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.019749363484246</v>
+        <v>3.552424872367026</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2745297331854208</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.908754439520587</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>4.161544549677852</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.743240521505836</v>
+        <v>3.14787831736501</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.411024810965523</v>
+        <v>1.011629153911424</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9784741728058788</v>
+        <v>3.552173554615833</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2061209196401016</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.866913073289897</v>
+        <v>4.287745515829901</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>4.202348812479487</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.740840483060152</v>
+        <v>3.145478278919327</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.404513844351211</v>
+        <v>1.018897699016924</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9786785210059206</v>
+        <v>3.552680934212349</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2061209196401016</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.864513034844213</v>
+        <v>4.285345477384217</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>4.202348812479487</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.737365202268397</v>
+        <v>3.145478278919327</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.385475716643914</v>
+        <v>1.018897699016924</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9828184912970845</v>
+        <v>3.552680934212349</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1479373083089071</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.826127587253742</v>
+        <v>4.285345477384217</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>4.202348812479487</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.856659603902588</v>
+        <v>3.145478278919327</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.416602347794532</v>
+        <v>1.018897699016924</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.089662240471027</v>
+        <v>3.552680934212349</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1479373083089071</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.945421988887932</v>
+        <v>4.285345477384217</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>4.202348812479487</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.857492932888721</v>
+        <v>3.145478278919327</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43046910912845</v>
+        <v>1.018897699016924</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.084948864923594</v>
+        <v>3.552680934212349</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1100793915750841</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.923540567833772</v>
+        <v>4.285345477384217</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>4.202348812479487</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.863501463285647</v>
+        <v>3.145478278919327</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.38566493758852</v>
+        <v>1.018897699016924</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.108879063936492</v>
+        <v>3.552680934212349</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1100793915750841</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.929549098230698</v>
+        <v>4.285345477384217</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>4.202348812479487</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.761451684562847</v>
+        <v>3.145478278919327</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.237921967353517</v>
+        <v>1.018897699016924</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.065926473307692</v>
+        <v>3.552680934212349</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2778867488099673</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.928183733848827</v>
+        <v>4.285345477384217</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>4.202348812479487</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.764245306094328</v>
+        <v>3.145478278919327</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.321743188628216</v>
+        <v>1.018897699016924</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.035191606329294</v>
+        <v>3.552680934212349</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2778867488099673</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.930977355380308</v>
+        <v>4.285345477384217</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>4.202348812479487</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.764907654485986</v>
+        <v>3.145478278919327</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.315590482575431</v>
+        <v>1.018897699016924</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.038315037142066</v>
+        <v>3.552680934212349</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2840394548627516</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.935331327403637</v>
+        <v>4.285345477384217</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>4.202348812479487</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.763988131226096</v>
+        <v>3.145478278919327</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.332399780725933</v>
+        <v>1.018897699016924</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.030671794621975</v>
+        <v>3.552680934212349</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2672301567122499</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.924326225253446</v>
+        <v>4.285345477384217</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>4.202348812479487</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.830323685022917</v>
+        <v>3.145478278919327</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.270101781949811</v>
+        <v>1.018897699016924</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.121926547929245</v>
+        <v>3.552680934212349</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2672301567122499</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.990661779050267</v>
+        <v>4.285345477384217</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>4.202348812479487</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.632615686737044</v>
+        <v>3.145478278919327</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.068311584284653</v>
+        <v>1.018897699016924</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.004934628709436</v>
+        <v>3.552680934212349</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4652483488814043</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.911764696065887</v>
+        <v>4.285345477384217</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>4.301006129572143</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.702905919059219</v>
+        <v>3.145478278919327</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.119198296970848</v>
+        <v>1.015773283084842</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.054870175957133</v>
+        <v>3.551431167839517</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4143616361952098</v>
+        <v>1.89977866410815</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.951522900776345</v>
+        <v>4.285345477384217</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>4.309071084658199</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.717533655175263</v>
+        <v>3.160106015035371</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.216938841595822</v>
+        <v>0.9189543247206278</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.030401694223187</v>
+        <v>3.527331320609874</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3984723580622296</v>
+        <v>1.88224677439211</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.956617070012601</v>
+        <v>4.289454079670636</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>4.309071084658199</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.716069635999935</v>
+        <v>3.160106015035371</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.277148139601107</v>
+        <v>0.9189543247206278</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.004853955845745</v>
+        <v>3.527331320609874</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3382630600569451</v>
+        <v>1.88224677439211</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.919027472034102</v>
+        <v>4.289454079670636</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>4.309071084658199</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.714561254039863</v>
+        <v>3.160106015035371</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.20072609316918</v>
+        <v>0.9189543247206278</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.033914392458444</v>
+        <v>3.527331320609874</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3382630600569451</v>
+        <v>1.88224677439211</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.91751909007403</v>
+        <v>4.289454079670636</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>4.309071084658199</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.714424121475299</v>
+        <v>3.160106015035371</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.156352961530612</v>
+        <v>0.9189543247206278</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.051526512549307</v>
+        <v>3.527331320609874</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3826361916955137</v>
+        <v>1.88224677439211</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.944005836492608</v>
+        <v>4.289454079670636</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>4.281131852972788</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.70881791561389</v>
+        <v>3.160106015035371</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.178833312389497</v>
+        <v>0.9269082950154001</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.036928166344344</v>
+        <v>3.530512908727784</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4151281033338745</v>
+        <v>1.88224677439211</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.957894777614215</v>
+        <v>4.289454079670636</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>4.292580884057146</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.715199672641694</v>
+        <v>3.166487772063175</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.131177581828441</v>
+        <v>0.9745640255764557</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.062372215596571</v>
+        <v>3.55595695798001</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4627838338949302</v>
+        <v>1.929902504953166</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.992869972978653</v>
+        <v>4.324429275035075</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>4.16501288659792</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.720092046016419</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.030659423329686</v>
+        <v>1.081595459914701</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.107471852370798</v>
+        <v>3.603661905090033</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5633019923936847</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.058073241452631</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>4.16501288659792</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.706846718492292</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.091326013732075</v>
+        <v>1.081595459914701</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.069959888685714</v>
+        <v>3.603661905090033</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4816036756751511</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.995808923897382</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>4.16501288659792</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.71094442110292</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.046487612123677</v>
+        <v>1.081595459914701</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.091992951939702</v>
+        <v>3.603661905090033</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4861471086200205</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.002632686274933</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>4.16501288659792</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.715105360733998</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.065986068365685</v>
+        <v>1.081595459914701</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.088354509073977</v>
+        <v>3.603661905090033</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4380624673401162</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.977942841138068</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>4.16501288659792</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.720984963261835</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.021783231279785</v>
+        <v>1.081595459914701</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.111915246436174</v>
+        <v>3.603661905090033</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4822653044260167</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.010344145917446</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>4.16501288659792</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.719394963731083</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.058762258943228</v>
+        <v>1.081595459914701</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.095533635840044</v>
+        <v>3.603661905090033</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5192392062173472</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.030938487461492</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>4.16501288659792</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.770642728914122</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.900470841403955</v>
+        <v>1.081595459914701</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.210097968038793</v>
+        <v>3.603661905090033</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5192392062173472</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.082186252644531</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>4.16501288659792</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.769083433508376</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.692828837769479</v>
+        <v>1.081595459914701</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.291595474086837</v>
+        <v>3.603661905090033</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7268812098518234</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.20521215941947</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>4.16501288659792</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.764031661746646</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.641796745046951</v>
+        <v>1.081595459914701</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.306956539414118</v>
+        <v>3.603661905090033</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7779133025743513</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.230779643291257</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>4.16501288659792</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.781219065839351</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.576572563919745</v>
+        <v>1.081595459914701</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.350233615957705</v>
+        <v>3.603661905090033</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8431374837015569</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.287101556060285</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>4.16501288659792</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.777180038138631</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.539145543848611</v>
+        <v>1.081595459914701</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.361165396285439</v>
+        <v>3.603661905090033</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8483890217307386</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.286213451177074</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>4.16501288659792</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.778436830469871</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.55925719988332</v>
+        <v>1.081595459914701</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.354377526202796</v>
+        <v>3.603661905090033</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8594163667281578</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.294086650506766</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>4.16501288659792</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.938994601491082</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.505512385456115</v>
+        <v>1.081595459914701</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.536433222994889</v>
+        <v>3.603661905090033</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8694796761686198</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.460682407192254</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>4.16501288659792</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.059107510708899</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.430730124431102</v>
+        <v>1.081595459914701</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.686459036622711</v>
+        <v>3.603661905090033</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9442619371936324</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.625664673025079</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>4.288678101227712</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.050815486722758</v>
+        <v>3.1713801454379</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.404646040167294</v>
+        <v>1.08429674140647</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.688600646342093</v>
+        <v>3.604742417686741</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9442619371936324</v>
+        <v>2.036933939291411</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.617372649038938</v>
+        <v>4.393540509012747</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>4.197044094829781</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.049008682306538</v>
+        <v>3.16957334102168</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.326514859318348</v>
+        <v>1.164556448233739</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.718046314265451</v>
+        <v>3.635039496001428</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.018438748077317</v>
+        <v>2.111322140003834</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.660071931152928</v>
+        <v>4.43636662502398</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>4.197044094829781</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.066563088033329</v>
+        <v>3.16957334102168</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.317622397925065</v>
+        <v>1.164556448233739</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.739157704549556</v>
+        <v>3.635039496001428</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.018438748077317</v>
+        <v>2.111322140003834</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.677626336879719</v>
+        <v>4.43636662502398</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>4.197044094829781</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.058418135437913</v>
+        <v>3.16957334102168</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.486098514894942</v>
+        <v>1.164556448233739</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.663622305166189</v>
+        <v>3.635039496001428</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9904909123607362</v>
+        <v>2.111322140003834</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.652712682854355</v>
+        <v>4.43636662502398</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>4.197044094829781</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.039687832625775</v>
+        <v>3.16957334102168</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.788298986033359</v>
+        <v>1.164556448233739</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.924011813898684</v>
+        <v>3.635039496001428</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9201428529903255</v>
+        <v>2.111322140003834</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.59177354441997</v>
+        <v>4.43636662502398</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>4.197044094829781</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.030351855122679</v>
+        <v>3.16957334102168</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.765577882350207</v>
+        <v>1.164556448233739</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.92376427786885</v>
+        <v>3.635039496001428</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9201428529903255</v>
+        <v>2.111322140003834</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.582437566916875</v>
+        <v>4.43636662502398</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>4.197044094829781</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.189257980973848</v>
+        <v>3.16957334102168</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.894779695644249</v>
+        <v>1.164556448233739</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.030989678402402</v>
+        <v>3.635039496001428</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7909410396962833</v>
+        <v>2.111322140003834</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.663822604791619</v>
+        <v>4.43636662502398</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>4.197044094829781</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.226335803467495</v>
+        <v>3.16957334102168</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.049560702422505</v>
+        <v>1.164556448233739</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.006155098184746</v>
+        <v>3.635039496001428</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7575733656418071</v>
+        <v>2.111322140003834</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.680879822852579</v>
+        <v>4.43636662502398</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>4.197044094829781</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.22301115945704</v>
+        <v>3.16957334102168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.042506012207331</v>
+        <v>1.164556448233739</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.00565233026036</v>
+        <v>3.635039496001428</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7646280558569809</v>
+        <v>2.111322140003834</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.681787992971229</v>
+        <v>4.43636662502398</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>4.197044094829781</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.233017313101782</v>
+        <v>3.16957334102168</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.015554787880843</v>
+        <v>1.164556448233739</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.026438973635697</v>
+        <v>3.635039496001428</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7795084018847001</v>
+        <v>2.111322140003834</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.700722354232602</v>
+        <v>4.43636662502398</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>4.197044094829781</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.417120445246741</v>
+        <v>3.16957334102168</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.151507795937159</v>
+        <v>1.164556448233739</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.15616090255813</v>
+        <v>3.635039496001428</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7795084018847001</v>
+        <v>2.111322140003834</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.884825486377562</v>
+        <v>4.43636662502398</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>4.222660019922719</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.409237140149735</v>
+        <v>3.16957334102168</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.173915913742031</v>
+        <v>1.166569951599757</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.139314350339175</v>
+        <v>3.635844897347835</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7795084018847001</v>
+        <v>2.111322140003834</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.876942181280555</v>
+        <v>4.43636662502398</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>4.193566768037636</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.411291139699372</v>
+        <v>3.171627340571317</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.321921681221431</v>
+        <v>1.021360275791089</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.082166042897052</v>
+        <v>3.579815026574005</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6927813930211586</v>
+        <v>2.025813597195189</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.826959975512067</v>
+        <v>4.387115498888431</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.913967520808999</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.467544857421219</v>
+        <v>3.171627340571317</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.331362607109961</v>
+        <v>1.021360275791089</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.134643390263487</v>
+        <v>3.579815026574005</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.81520851056455</v>
+        <v>2.025813597195189</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.956669963759949</v>
+        <v>4.387115498888431</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.913967520808999</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.47043595196652</v>
+        <v>3.171627340571317</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.383636214445602</v>
+        <v>1.021360275791089</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.116625041874532</v>
+        <v>3.579815026574005</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7629349032289088</v>
+        <v>2.025813597195189</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.928196893903865</v>
+        <v>4.387115498888431</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.913967520808999</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.468547764860295</v>
+        <v>3.171627340571317</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.459966192046508</v>
+        <v>1.021360275791089</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.084204863727945</v>
+        <v>3.579815026574005</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7629349032289088</v>
+        <v>2.025813597195189</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.926308706797641</v>
+        <v>4.387115498888431</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.913967520808999</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.463367994463157</v>
+        <v>3.171627340571317</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.662219912370861</v>
+        <v>1.021360275791089</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.998123605201066</v>
+        <v>3.579815026574005</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5606811829045553</v>
+        <v>2.025813597195189</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.799776704205891</v>
+        <v>4.387115498888431</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.913967520808999</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.46180200467331</v>
+        <v>3.171627340571317</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.823788337898117</v>
+        <v>1.021360275791089</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.931930245200316</v>
+        <v>3.579815026574005</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4338982591066759</v>
+        <v>2.025813597195189</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.722140960137315</v>
+        <v>4.387115498888431</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.913967520808999</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.474875411539228</v>
+        <v>3.171627340571317</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.95608962999567</v>
+        <v>1.021360275791089</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.892083135227213</v>
+        <v>3.579815026574005</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4338982591066759</v>
+        <v>2.025813597195189</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.735214367003234</v>
+        <v>4.387115498888431</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>4.349971443633434</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.474875411539228</v>
+        <v>3.171627340571317</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.95765127281053</v>
+        <v>1.019798632976229</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.891458478101269</v>
+        <v>3.579190369448061</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4338982591066759</v>
+        <v>2.025813597195189</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.735214367003234</v>
+        <v>4.387115498888431</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.47339945266623</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.985552059920003</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.878822204384482</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3993013349637411</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.712980253644475</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.470163896643429</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.108078162622897</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.826576207280523</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2767752322608472</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.636229035999938</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.536869856233933</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.338592658808486</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.801076368396791</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.04626073607525849</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.564626297879088</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.67718157523578</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.595313476803311</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.838699760200708</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.06215383806855634</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.639889272394647</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.74616184438142</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.749299894579451</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.846085462235892</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.06215383806855634</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.708869541540286</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.732213046501541</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.698777990751785</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.852345425887079</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.06215383806855634</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.694920743660407</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.744083535556955</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.95125314475951</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.763225853339403</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.06215383806855634</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.706791232715821</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.745294070075898</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.244148901238922</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.647278085266582</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.06215383806855634</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.708001767234765</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637086</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.74941581230322</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.401692972968363</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.588382198802127</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1290556432088308</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.671982426377922</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.744493665039409</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.679657368551637</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.472274293305007</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2186753774943151</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.613288438542821</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.906697721738453</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.796625061190528</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.587691272948495</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2186753774943151</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.775492495241865</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.901544359702267</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.881343003411481</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.548650734023928</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.3037914064223615</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.719269515848851</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253287</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.911773777270759</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.963277821680364</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.526106224284866</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3137261520094417</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.723538086065094</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717831</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.920699415726661</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.065253943928772</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.494241413841405</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4157022742578492</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.671278051171952</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.912852302970836</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.95524766045155</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.530396814476469</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.392497702340574</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.677353681566492</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203661</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.917102313692811</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.812188084710625</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.591870655494813</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.3844842757505947</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.686411748242454</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436927</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.924363196575347</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.510741359238787</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.719710228566084</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.08303755027875748</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.874540666408092</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.925334374328057</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.535331603473971</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.710845308624721</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.08303755027875748</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.875511844160803</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859299</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.926177278707812</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.484293227467451</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.732103563407084</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.08303755027875748</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.876354748540558</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354683</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.945215377581958</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.44315393260082</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.767597380227882</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.04189825541212666</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.920076424334682</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085618</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.761399373705892</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.332547792521218</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.628023832383658</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.06870788466747535</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.802624104506378</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80470312146278</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.764901417779856</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.463128527052061</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.579293582645284</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.06187284986336716</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.727777707861836</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218598</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.749328236855939</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.298632192861099</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.629518935397752</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.06187284986336716</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.712204526937918</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462767</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.748515947292368</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.326002125545531</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.617758672760409</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.06187284986336716</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.711392237374348</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533049</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.758384726417441</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.336387320435421</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.623473373929525</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.07225804475325648</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.715029899565487</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120423</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.829221732193866</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.354975479157646</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.686875116217061</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.09084620347548183</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.774714010108577</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855134695881693</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.826090743012164</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.355274025853682</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.683624708356945</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.09084620347548183</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.771583020926875</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815657372493997</v>
+        <v>4.409480289874755</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.830621637951556</v>
+        <v>3.170151381698319</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.254450892163254</v>
+        <v>0.9862832614152426</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.728484856772507</v>
+        <v>3.564308261950669</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.078381987991128</v>
+        <v>1.986737464424265</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.783592445156879</v>
+        <v>4.362193860352878</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.478283254493701</v>
+        <v>4.396804193744029</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.830750891430099</v>
+        <v>3.170280635176862</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.29225475873455</v>
+        <v>0.967627403864443</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.713492563622532</v>
+        <v>3.556975172408892</v>
       </c>
       <c r="F2041" t="n">
-        <v>-0.1161858545624236</v>
+        <v>1.985936726388033</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.761039378692645</v>
+        <v>4.361842671009683</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240731.xlsx
+++ b/tame_output/ON/bt/strategyON_20240731.xlsx
@@ -605,17 +605,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>441</v>
+        <v>342</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>111.6%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,55 +791,55 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>-80.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>111.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,17 +949,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>126.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -969,35 +969,35 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-106.2%</t>
+          <t>-640.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,32 +1007,32 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>439.0%</t>
+          <t>454.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-64.8%</t>
+          <t>-686.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1127,35 +1127,35 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-40.3%</t>
+          <t>-256.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>-153.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-203.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1285,20 +1285,20 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-57.2%</t>
+          <t>-262.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,32 +1323,32 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
         <is>
           <t>-0.3</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-149.1%</t>
+          <t>-132.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-231.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>106.4%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,20 +1443,20 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-19</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-158.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>105.4%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-68.5%</t>
         </is>
       </c>
     </row>
@@ -43773,22 +43773,22 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.825905229988204</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
-        <v>3.138175778137954</v>
+        <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.5532457673970779</v>
+        <v>0.3997263829116132</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.359117660783038</v>
+        <v>3.2775351796163</v>
       </c>
       <c r="F1836" t="n">
         <v>1.668418790368211</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.139227052358882</v>
+        <v>4.119052324986328</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.825905229988204</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
-        <v>3.138175778137954</v>
+        <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.5532457673970779</v>
+        <v>0.3243370297764078</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.359117660783038</v>
+        <v>3.247868577088092</v>
       </c>
       <c r="F1837" t="n">
         <v>1.668418790368211</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.139227052358882</v>
+        <v>4.119541463712203</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.825905229988204</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
-        <v>3.138175778137954</v>
+        <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.5532457673970779</v>
+        <v>0.1878921395489951</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.359117660783038</v>
+        <v>3.197370603618793</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.668418790368211</v>
+        <v>1.531973900140798</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.139227052358882</v>
+        <v>4.041754512197421</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.825905229988204</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
-        <v>3.138175778137954</v>
+        <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.5532457673970779</v>
+        <v>-0.04923935230080001</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.359117660783038</v>
+        <v>3.137459091376417</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.668418790368211</v>
+        <v>1.531973900140798</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.139227052358882</v>
+        <v>4.076695596694964</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.825905229988204</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
-        <v>3.138175778137954</v>
+        <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.5532457673970779</v>
+        <v>-0.04420176157321348</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.359117660783038</v>
+        <v>3.13805156785279</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.668418790368211</v>
+        <v>1.587618356407115</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.139227052358882</v>
+        <v>4.108659710640092</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.825905229988204</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
-        <v>3.138175778137954</v>
+        <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.5532457673970779</v>
+        <v>-0.3013957962812702</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.359117660783038</v>
+        <v>3.013920335593304</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.668418790368211</v>
+        <v>1.330424321699059</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.139227052358882</v>
+        <v>3.933089671438995</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.825905229988204</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
-        <v>3.138175778137954</v>
+        <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.5532457673970779</v>
+        <v>-0.3671631863306823</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.359117660783038</v>
+        <v>2.988630988704009</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.668418790368211</v>
+        <v>1.330424321699059</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.139227052358882</v>
+        <v>3.934107280569465</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.825905229988204</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
-        <v>3.138175778137954</v>
+        <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.5532457673970779</v>
+        <v>-0.5724078633879268</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.359117660783038</v>
+        <v>2.897161149868867</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.668418790368211</v>
+        <v>1.330424321699059</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.139227052358882</v>
+        <v>3.924735312557221</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.825905229988204</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
-        <v>3.138175778137954</v>
+        <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.5532457673970779</v>
+        <v>-0.6541797638156785</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.359117660783038</v>
+        <v>2.854535115653005</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.668418790368211</v>
+        <v>1.357459895105195</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.139227052358882</v>
+        <v>3.931039382556141</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.825905229988204</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
-        <v>3.138175778137954</v>
+        <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.5532457673970779</v>
+        <v>-0.7213888716875563</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.359117660783038</v>
+        <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.668418790368211</v>
+        <v>1.357459895105195</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.139227052358882</v>
+        <v>3.935804699389843</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.825905229988204</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
-        <v>3.138175778137954</v>
+        <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.5532457673970779</v>
+        <v>-0.7099996350327549</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.359117660783038</v>
+        <v>2.834797280119117</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.668418790368211</v>
+        <v>1.368849131759997</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.139227052358882</v>
+        <v>3.940463037501964</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.825905229988204</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
-        <v>3.138175778137954</v>
+        <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>0.5532457673970779</v>
+        <v>-1.127753658579592</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.359117660783038</v>
+        <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.668418790368211</v>
+        <v>0.9510951082131597</v>
       </c>
       <c r="G1847" t="n">
-        <v>4.139227052358882</v>
+        <v>3.687737514878926</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.825905229988204</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
-        <v>3.138175778137954</v>
+        <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>0.5532457673970779</v>
+        <v>-1.417885325185023</v>
       </c>
       <c r="E1848" t="n">
-        <v>3.359117660783038</v>
+        <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.668418790368211</v>
+        <v>0.9751769029533396</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.139227052358882</v>
+        <v>3.702052808321955</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.825905229988204</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
-        <v>3.138175778137954</v>
+        <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>0.5532457673970779</v>
+        <v>-1.625889383538101</v>
       </c>
       <c r="E1849" t="n">
-        <v>3.359117660783038</v>
+        <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.668418790368211</v>
+        <v>0.9751769029533396</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.139227052358882</v>
+        <v>3.70694495287588</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.825905229988204</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
-        <v>3.138175778137954</v>
+        <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>0.5532457673970779</v>
+        <v>-1.688067794699071</v>
       </c>
       <c r="E1850" t="n">
-        <v>3.359117660783038</v>
+        <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.668418790368211</v>
+        <v>0.9129984917923695</v>
       </c>
       <c r="G1850" t="n">
-        <v>4.139227052358882</v>
+        <v>3.664719362517286</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.825905229988204</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
-        <v>3.138175778137954</v>
+        <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>0.5532457673970779</v>
+        <v>-2.054136521843724</v>
       </c>
       <c r="E1851" t="n">
-        <v>3.359117660783038</v>
+        <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
-        <v>1.668418790368211</v>
+        <v>0.5469297646477168</v>
       </c>
       <c r="G1851" t="n">
-        <v>4.139227052358882</v>
+        <v>3.438162425536944</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.825905229988204</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
-        <v>3.138175778137954</v>
+        <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>0.5532457673970779</v>
+        <v>-2.262627303295408</v>
       </c>
       <c r="E1852" t="n">
-        <v>3.359117660783038</v>
+        <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
-        <v>1.668418790368211</v>
+        <v>0.3384389831960324</v>
       </c>
       <c r="G1852" t="n">
-        <v>4.139227052358882</v>
+        <v>3.333406246404702</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.825905229988204</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
-        <v>3.138175778137954</v>
+        <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>0.5532457673970779</v>
+        <v>-2.50982848806063</v>
       </c>
       <c r="E1853" t="n">
-        <v>3.359117660783038</v>
+        <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
-        <v>1.668418790368211</v>
+        <v>0.3585923366948448</v>
       </c>
       <c r="G1853" t="n">
-        <v>4.139227052358882</v>
+        <v>3.353597008912558</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.825905229988204</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
-        <v>3.138175778137954</v>
+        <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>0.5532457673970779</v>
+        <v>-3.002213516084727</v>
       </c>
       <c r="E1854" t="n">
-        <v>3.359117660783038</v>
+        <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
-        <v>1.668418790368211</v>
+        <v>-0.1337926913292519</v>
       </c>
       <c r="G1854" t="n">
-        <v>4.139227052358882</v>
+        <v>3.059272384141832</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.825905229988204</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
-        <v>3.138175778137954</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>0.5532457673970779</v>
+        <v>-3.387393907014799</v>
       </c>
       <c r="E1855" t="n">
-        <v>3.359117660783038</v>
+        <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
-        <v>1.668418790368211</v>
+        <v>-0.1337926913292519</v>
       </c>
       <c r="G1855" t="n">
-        <v>4.139227052358882</v>
+        <v>3.057814922954695</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.825905229988204</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.138175778137954</v>
+        <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>0.5532457673970779</v>
+        <v>-3.637264587029381</v>
       </c>
       <c r="E1856" t="n">
-        <v>3.359117660783038</v>
+        <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
-        <v>1.668418790368211</v>
+        <v>-0.09752997149878867</v>
       </c>
       <c r="G1856" t="n">
-        <v>4.139227052358882</v>
+        <v>3.081341678307589</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.825905229988204</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.138175778137954</v>
+        <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>0.5532457673970779</v>
+        <v>-3.843776363916402</v>
       </c>
       <c r="E1857" t="n">
-        <v>3.359117660783038</v>
+        <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
-        <v>1.668418790368211</v>
+        <v>-0.3040417483858102</v>
       </c>
       <c r="G1857" t="n">
-        <v>4.139227052358882</v>
+        <v>2.953540670831634</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.825905229988204</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.138175778137954</v>
+        <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>0.5532457673970779</v>
+        <v>-4.163120438996904</v>
       </c>
       <c r="E1858" t="n">
-        <v>3.359117660783038</v>
+        <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
-        <v>1.668418790368211</v>
+        <v>-0.3040417483858102</v>
       </c>
       <c r="G1858" t="n">
-        <v>4.139227052358882</v>
+        <v>2.955313597531894</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.825905229988204</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.138175778137954</v>
+        <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>0.5532457673970779</v>
+        <v>-4.549330270272679</v>
       </c>
       <c r="E1859" t="n">
-        <v>3.359117660783038</v>
+        <v>1.303983001607965</v>
       </c>
       <c r="F1859" t="n">
-        <v>1.668418790368211</v>
+        <v>-0.3948146881032535</v>
       </c>
       <c r="G1859" t="n">
-        <v>4.139227052358882</v>
+        <v>2.887182721168832</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.825905229988204</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.138175778137954</v>
+        <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>0.5532457673970779</v>
+        <v>-4.784024264405232</v>
       </c>
       <c r="E1860" t="n">
-        <v>3.359117660783038</v>
+        <v>1.198390178957035</v>
       </c>
       <c r="F1860" t="n">
-        <v>1.668418790368211</v>
+        <v>-0.3884784208739983</v>
       </c>
       <c r="G1860" t="n">
-        <v>4.139227052358882</v>
+        <v>2.879269256508476</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.825905229988204</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.138175778137954</v>
+        <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>0.5532457673970779</v>
+        <v>-5.119686911635684</v>
       </c>
       <c r="E1861" t="n">
-        <v>3.359117660783038</v>
+        <v>1.062705711720819</v>
       </c>
       <c r="F1861" t="n">
-        <v>1.668418790368211</v>
+        <v>-0.4564094063629031</v>
       </c>
       <c r="G1861" t="n">
-        <v>4.139227052358882</v>
+        <v>2.837091256871098</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.825905229988204</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.138175778137954</v>
+        <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>0.5532457673970779</v>
+        <v>-5.196131241838556</v>
       </c>
       <c r="E1862" t="n">
-        <v>3.359117660783038</v>
+        <v>1.038615539873912</v>
       </c>
       <c r="F1862" t="n">
-        <v>1.668418790368211</v>
+        <v>-0.3759638972692412</v>
       </c>
       <c r="G1862" t="n">
-        <v>4.139227052358882</v>
+        <v>2.891846122561537</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.825905229988204</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.138175778137954</v>
+        <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>0.5532457673970779</v>
+        <v>-5.561258624477302</v>
       </c>
       <c r="E1863" t="n">
-        <v>3.359117660783038</v>
+        <v>0.8918191018242445</v>
       </c>
       <c r="F1863" t="n">
-        <v>1.668418790368211</v>
+        <v>-0.6722746815682538</v>
       </c>
       <c r="G1863" t="n">
-        <v>4.139227052358882</v>
+        <v>2.713314166987961</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.825905229988204</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.138175778137954</v>
+        <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>0.5532457673970779</v>
+        <v>-5.969847401657981</v>
       </c>
       <c r="E1864" t="n">
-        <v>3.359117660783038</v>
+        <v>0.7271451349667317</v>
       </c>
       <c r="F1864" t="n">
-        <v>1.668418790368211</v>
+        <v>-1.080863458748932</v>
       </c>
       <c r="G1864" t="n">
-        <v>4.139227052358882</v>
+        <v>2.466922444694313</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.825905229988204</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.138175778137954</v>
+        <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>0.5532457673970779</v>
+        <v>-6.083607813680846</v>
       </c>
       <c r="E1865" t="n">
-        <v>3.359117660783038</v>
+        <v>0.6768264026290467</v>
       </c>
       <c r="F1865" t="n">
-        <v>1.668418790368211</v>
+        <v>-1.080863458748932</v>
       </c>
       <c r="G1865" t="n">
-        <v>4.139227052358882</v>
+        <v>2.462107877165773</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.825905229988204</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.138175778137954</v>
+        <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>0.5532457673970779</v>
+        <v>-6.499999687967843</v>
       </c>
       <c r="E1866" t="n">
-        <v>3.359117660783038</v>
+        <v>0.508263703523125</v>
       </c>
       <c r="F1866" t="n">
-        <v>1.668418790368211</v>
+        <v>-1.080863458748932</v>
       </c>
       <c r="G1866" t="n">
-        <v>4.139227052358882</v>
+        <v>2.460101927774651</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.825905229988204</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.138175778137954</v>
+        <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>0.5532457673970779</v>
+        <v>-6.861173317784831</v>
       </c>
       <c r="E1867" t="n">
-        <v>3.359117660783038</v>
+        <v>0.374052942265009</v>
       </c>
       <c r="F1867" t="n">
-        <v>1.668418790368211</v>
+        <v>-1.080863458748932</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.139227052358882</v>
+        <v>2.47036061844333</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.825905229988204</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.138175778137954</v>
+        <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>0.5532457673970779</v>
+        <v>-7.20443183742785</v>
       </c>
       <c r="E1868" t="n">
-        <v>3.359117660783038</v>
+        <v>0.2328490995534964</v>
       </c>
       <c r="F1868" t="n">
-        <v>1.668418790368211</v>
+        <v>-1.080863458748932</v>
       </c>
       <c r="G1868" t="n">
-        <v>4.139227052358882</v>
+        <v>2.466460183589025</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.825905229988204</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.138175778137954</v>
+        <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>0.5532457673970779</v>
+        <v>-7.252634654670194</v>
       </c>
       <c r="E1869" t="n">
-        <v>3.359117660783038</v>
+        <v>0.2119728927115596</v>
       </c>
       <c r="F1869" t="n">
-        <v>1.668418790368211</v>
+        <v>-1.080863458748932</v>
       </c>
       <c r="G1869" t="n">
-        <v>4.139227052358882</v>
+        <v>2.464865103644026</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.825905229988204</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.138175778137954</v>
+        <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>0.5532457673970779</v>
+        <v>-7.549295996480391</v>
       </c>
       <c r="E1870" t="n">
-        <v>3.359117660783038</v>
+        <v>0.09708733191668895</v>
       </c>
       <c r="F1870" t="n">
-        <v>1.668418790368211</v>
+        <v>-1.149606594482811</v>
       </c>
       <c r="G1870" t="n">
-        <v>4.139227052358882</v>
+        <v>2.427398198132907</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.825905229988204</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.138175778137954</v>
+        <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>0.5532457673970779</v>
+        <v>-7.736015704789694</v>
       </c>
       <c r="E1871" t="n">
-        <v>3.359117660783038</v>
+        <v>0.01837314405856461</v>
       </c>
       <c r="F1871" t="n">
-        <v>1.668418790368211</v>
+        <v>-1.149606594482811</v>
       </c>
       <c r="G1871" t="n">
-        <v>4.139227052358882</v>
+        <v>2.423371893598504</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.825905229988204</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.138175778137954</v>
+        <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>0.5532457673970779</v>
+        <v>-8.119017093532324</v>
       </c>
       <c r="E1872" t="n">
-        <v>3.359117660783038</v>
+        <v>-0.1349295127600714</v>
       </c>
       <c r="F1872" t="n">
-        <v>1.668418790368211</v>
+        <v>-1.149606594482811</v>
       </c>
       <c r="G1872" t="n">
-        <v>4.139227052358882</v>
+        <v>2.42326979227692</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.825905229988204</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.138175778137954</v>
+        <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>0.5532457673970779</v>
+        <v>-8.123503538733713</v>
       </c>
       <c r="E1873" t="n">
-        <v>3.359117660783038</v>
+        <v>-0.1341525748691965</v>
       </c>
       <c r="F1873" t="n">
-        <v>1.668418790368211</v>
+        <v>-1.154093039684199</v>
       </c>
       <c r="G1873" t="n">
-        <v>4.139227052358882</v>
+        <v>2.423149441127517</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.825905229988204</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.138175778137954</v>
+        <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>0.5532457673970779</v>
+        <v>-8.483033861237715</v>
       </c>
       <c r="E1874" t="n">
-        <v>3.359117660783038</v>
+        <v>-0.2726144005727473</v>
       </c>
       <c r="F1874" t="n">
-        <v>1.668418790368211</v>
+        <v>-1.154093039684199</v>
       </c>
       <c r="G1874" t="n">
-        <v>4.139227052358882</v>
+        <v>2.428499744425567</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.825905229988204</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.138175778137954</v>
+        <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>0.5532457673970779</v>
+        <v>-8.533382924691937</v>
       </c>
       <c r="E1875" t="n">
-        <v>3.359117660783038</v>
+        <v>-0.2848380059972584</v>
       </c>
       <c r="F1875" t="n">
-        <v>1.668418790368211</v>
+        <v>-1.204442103138421</v>
       </c>
       <c r="G1875" t="n">
-        <v>4.139227052358882</v>
+        <v>2.406206326310211</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.825905229988204</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.138175778137954</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>0.5532457673970779</v>
+        <v>-8.631002202113333</v>
       </c>
       <c r="E1876" t="n">
-        <v>3.359117660783038</v>
+        <v>-0.3208439663440479</v>
       </c>
       <c r="F1876" t="n">
-        <v>1.668418790368211</v>
+        <v>-1.302061380559818</v>
       </c>
       <c r="G1876" t="n">
-        <v>4.139227052358882</v>
+        <v>2.350676510479142</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.604631100061017</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.138175778137954</v>
+        <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>0.5569366923534892</v>
+        <v>-8.685073701621691</v>
       </c>
       <c r="E1877" t="n">
-        <v>3.360594030765603</v>
+        <v>-0.3395790098258193</v>
       </c>
       <c r="F1877" t="n">
-        <v>1.668418790368211</v>
+        <v>-1.356132880068178</v>
       </c>
       <c r="G1877" t="n">
-        <v>4.139227052358882</v>
+        <v>2.321127167095698</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.61497278726522</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.143688975256597</v>
+        <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>0.3526785170236256</v>
+        <v>-8.889331876951555</v>
       </c>
       <c r="E1878" t="n">
-        <v>3.2844039577523</v>
+        <v>-0.4157690828391223</v>
       </c>
       <c r="F1878" t="n">
-        <v>1.540779845754222</v>
+        <v>-1.483771824682167</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.06815688270913</v>
+        <v>2.250056997445947</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.609034292853409</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.148171529741033</v>
+        <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>0.3190256785151517</v>
+        <v>-8.922984715460029</v>
       </c>
       <c r="E1879" t="n">
-        <v>3.275425376833346</v>
+        <v>-0.4247476637580756</v>
       </c>
       <c r="F1879" t="n">
-        <v>1.440366477837185</v>
+        <v>-1.584185192599204</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.012391416443344</v>
+        <v>2.194291531180161</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.461454158459341</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.163543231234454</v>
+        <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>0.3871567198501421</v>
+        <v>-8.84951488379258</v>
       </c>
       <c r="E1880" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.379988029597675</v>
       </c>
       <c r="F1880" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.510715360931755</v>
       </c>
       <c r="G1880" t="n">
-        <v>4.068641742737759</v>
+        <v>2.253745131674051</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.461454158459341</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.163543231234454</v>
+        <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>0.3871567198501421</v>
+        <v>-9.024639301179123</v>
       </c>
       <c r="E1881" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.4354825758047758</v>
       </c>
       <c r="F1881" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.685839778318299</v>
       </c>
       <c r="G1881" t="n">
-        <v>4.068641742737759</v>
+        <v>2.163225701989642</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.461454158459341</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.163543231234454</v>
+        <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>0.3871567198501421</v>
+        <v>-9.259091395193613</v>
       </c>
       <c r="E1882" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.5364825783121674</v>
       </c>
       <c r="F1882" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.685839778318299</v>
       </c>
       <c r="G1882" t="n">
-        <v>4.068641742737759</v>
+        <v>2.156006537088046</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.461454158459341</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.163543231234454</v>
+        <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>0.3871567198501421</v>
+        <v>-9.363466126220059</v>
       </c>
       <c r="E1883" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.5849046614967222</v>
       </c>
       <c r="F1883" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.790214509344745</v>
       </c>
       <c r="G1883" t="n">
-        <v>4.068641742737759</v>
+        <v>2.086709507698202</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.461454158459341</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.163543231234454</v>
+        <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>0.3871567198501421</v>
+        <v>-9.416252281820386</v>
       </c>
       <c r="E1884" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.6049033338982968</v>
       </c>
       <c r="F1884" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.885889995927142</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.068641742737759</v>
+        <v>2.03042000558732</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.461454158459341</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.163543231234454</v>
+        <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>0.3871567198501421</v>
+        <v>-9.542289075188675</v>
       </c>
       <c r="E1885" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.6526243226164978</v>
       </c>
       <c r="F1885" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.8606383731174</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.068641742737759</v>
+        <v>2.04826470790228</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.461454158459341</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.163543231234454</v>
+        <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>0.3871567198501421</v>
+        <v>-9.485217303292744</v>
       </c>
       <c r="E1886" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.6258052781717245</v>
       </c>
       <c r="F1886" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.8606383731174</v>
       </c>
       <c r="G1886" t="n">
-        <v>4.068641742737759</v>
+        <v>2.052255043588681</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.461454158459341</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.163543231234454</v>
+        <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>0.3871567198501421</v>
+        <v>-9.626889145016865</v>
       </c>
       <c r="E1887" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.6839492417601143</v>
       </c>
       <c r="F1887" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.8606383731174</v>
       </c>
       <c r="G1887" t="n">
-        <v>4.068641742737759</v>
+        <v>2.050779816689939</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.461454158459341</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.163543231234454</v>
+        <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>0.3871567198501421</v>
+        <v>-9.57729830059203</v>
       </c>
       <c r="E1888" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.6490594938253085</v>
       </c>
       <c r="F1888" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.811047528692566</v>
       </c>
       <c r="G1888" t="n">
-        <v>4.068641742737759</v>
+        <v>2.095587733509712</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.461454158459341</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.163543231234454</v>
+        <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>0.3871567198501421</v>
+        <v>-9.428379966120174</v>
       </c>
       <c r="E1889" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.6025432936832487</v>
       </c>
       <c r="F1889" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.779797937957393</v>
       </c>
       <c r="G1889" t="n">
-        <v>4.068641742737759</v>
+        <v>2.101286354304133</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.461454158459341</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.163543231234454</v>
+        <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>0.3871567198501421</v>
+        <v>-9.202534813400764</v>
       </c>
       <c r="E1890" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.5026261595592758</v>
       </c>
       <c r="F1890" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.737871262370229</v>
       </c>
       <c r="G1890" t="n">
-        <v>4.068641742737759</v>
+        <v>2.136021432692639</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.461454158459341</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.163543231234454</v>
+        <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>0.3871567198501421</v>
+        <v>-9.077956157063172</v>
       </c>
       <c r="E1891" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.4516555524681802</v>
       </c>
       <c r="F1891" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.737871262370229</v>
       </c>
       <c r="G1891" t="n">
-        <v>4.068641742737759</v>
+        <v>2.137160577248698</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.461454158459341</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.163543231234454</v>
+        <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>0.3871567198501421</v>
+        <v>-9.130851445107458</v>
       </c>
       <c r="E1892" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.4701798935237873</v>
       </c>
       <c r="F1892" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.732915916281783</v>
       </c>
       <c r="G1892" t="n">
-        <v>4.068641742737759</v>
+        <v>2.142767559063874</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.461454158459341</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.163543231234454</v>
+        <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>0.3871567198501421</v>
+        <v>-9.058718269819577</v>
       </c>
       <c r="E1893" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.4355929191699985</v>
       </c>
       <c r="F1893" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.732915916281783</v>
       </c>
       <c r="G1893" t="n">
-        <v>4.068641742737759</v>
+        <v>2.14850126330251</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.461454158459341</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.163543231234454</v>
+        <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>0.3871567198501421</v>
+        <v>-8.98735187720993</v>
       </c>
       <c r="E1894" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.4167836245200047</v>
       </c>
       <c r="F1894" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.661549523672135</v>
       </c>
       <c r="G1894" t="n">
-        <v>4.068641742737759</v>
+        <v>2.181583836474434</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.461454158459341</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.163543231234454</v>
+        <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>0.3871567198501421</v>
+        <v>-8.893892843224705</v>
       </c>
       <c r="E1895" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.3892834922388224</v>
       </c>
       <c r="F1895" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.661549523672135</v>
       </c>
       <c r="G1895" t="n">
-        <v>4.068641742737759</v>
+        <v>2.171700355161526</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.461454158459341</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.163543231234454</v>
+        <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>0.3871567198501421</v>
+        <v>-8.883239661671274</v>
       </c>
       <c r="E1896" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.3868567801168235</v>
       </c>
       <c r="F1896" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.661549523672135</v>
       </c>
       <c r="G1896" t="n">
-        <v>4.068641742737759</v>
+        <v>2.169865794662153</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.461454158459341</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.163543231234454</v>
+        <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>0.3871567198501421</v>
+        <v>-8.785332622994783</v>
       </c>
       <c r="E1897" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.3479942796196882</v>
       </c>
       <c r="F1897" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.593563773811579</v>
       </c>
       <c r="G1897" t="n">
-        <v>4.068641742737759</v>
+        <v>2.210356929605025</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.461454158459341</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.163543231234454</v>
+        <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>0.3871567198501421</v>
+        <v>-8.761379082018825</v>
       </c>
       <c r="E1898" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.3377443570838112</v>
       </c>
       <c r="F1898" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.569610232835621</v>
       </c>
       <c r="G1898" t="n">
-        <v>4.068641742737759</v>
+        <v>2.225397560336094</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.461454158459341</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.163543231234454</v>
+        <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>0.3871567198501421</v>
+        <v>-8.497319143696028</v>
       </c>
       <c r="E1899" t="n">
-        <v>3.318049494860764</v>
+        <v>-0.2453806979164446</v>
       </c>
       <c r="F1899" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.305550294512825</v>
       </c>
       <c r="G1899" t="n">
-        <v>4.068641742737759</v>
+        <v>2.370573207168019</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.461454158459341</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.163543231234454</v>
+        <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>0.3871567198501421</v>
+        <v>-7.79023952019119</v>
       </c>
       <c r="E1900" t="n">
-        <v>3.318049494860764</v>
+        <v>0.03466411782518986</v>
       </c>
       <c r="F1900" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.305550294512825</v>
       </c>
       <c r="G1900" t="n">
-        <v>4.068641742737759</v>
+        <v>2.367786173507719</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.461454158459341</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.163543231234454</v>
+        <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>0.3871567198501421</v>
+        <v>-7.750055221825</v>
       </c>
       <c r="E1901" t="n">
-        <v>3.318049494860764</v>
+        <v>0.05108146105950739</v>
       </c>
       <c r="F1901" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.265365996146634</v>
       </c>
       <c r="G1901" t="n">
-        <v>4.068641742737759</v>
+        <v>2.392240376415274</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.461454158459341</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.163543231234454</v>
+        <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>0.3871567198501421</v>
+        <v>-7.586655350885637</v>
       </c>
       <c r="E1902" t="n">
-        <v>3.318049494860764</v>
+        <v>0.1158082306560093</v>
       </c>
       <c r="F1902" t="n">
-        <v>1.508497519172175</v>
+        <v>-1.101966125207272</v>
       </c>
       <c r="G1902" t="n">
-        <v>4.068641742737759</v>
+        <v>2.489647120199649</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>4.006902670095509</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.163543231234454</v>
+        <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>0.3984231136234098</v>
+        <v>-7.353174128656039</v>
       </c>
       <c r="E1903" t="n">
-        <v>3.322556052370071</v>
+        <v>0.2171251483857009</v>
       </c>
       <c r="F1903" t="n">
-        <v>1.508497519172175</v>
+        <v>-0.8684849029776731</v>
       </c>
       <c r="G1903" t="n">
-        <v>4.068641742737759</v>
+        <v>2.63766028237526</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>4.021209363589485</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.160651020921495</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>0.5480895046309247</v>
+        <v>-7.203507737648524</v>
       </c>
       <c r="E1904" t="n">
-        <v>3.379530398460117</v>
+        <v>0.274099494475748</v>
       </c>
       <c r="F1904" t="n">
-        <v>1.601401010414711</v>
+        <v>-0.7755814117351372</v>
       </c>
       <c r="G1904" t="n">
-        <v>4.121491627170322</v>
+        <v>2.690510166807822</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.769398491143837</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.156018507668522</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>0.7007501855493687</v>
+        <v>-7.071232264017637</v>
       </c>
       <c r="E1905" t="n">
-        <v>3.435962157574522</v>
+        <v>0.3223771706751295</v>
       </c>
       <c r="F1905" t="n">
-        <v>1.754061691333155</v>
+        <v>-0.6433059381042505</v>
       </c>
       <c r="G1905" t="n">
-        <v>4.208455522468415</v>
+        <v>2.765242937733382</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.769398491143837</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.156018507668522</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>0.7007501855493687</v>
+        <v>-6.915493931457895</v>
       </c>
       <c r="E1906" t="n">
-        <v>3.435962157574522</v>
+        <v>0.3874875643866629</v>
       </c>
       <c r="F1906" t="n">
-        <v>1.754061691333155</v>
+        <v>-0.487567605544509</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.208455522468415</v>
+        <v>2.861500997956863</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.769398491143837</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.156018507668522</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>0.7007501855493687</v>
+        <v>-6.666494132774314</v>
       </c>
       <c r="E1907" t="n">
-        <v>3.435962157574522</v>
+        <v>0.4999938250837541</v>
       </c>
       <c r="F1907" t="n">
-        <v>1.754061691333155</v>
+        <v>-0.2385678068609283</v>
       </c>
       <c r="G1907" t="n">
-        <v>4.208455522468415</v>
+        <v>3.023807218390671</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.769398491143837</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.156018507668522</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>0.7007501855493687</v>
+        <v>-6.772084122547419</v>
       </c>
       <c r="E1908" t="n">
-        <v>3.435962157574522</v>
+        <v>0.3297818995752935</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.754061691333155</v>
+        <v>-0.3441577966340326</v>
       </c>
       <c r="G1908" t="n">
-        <v>4.208455522468415</v>
+        <v>2.832477294927589</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.769398491143837</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.156018507668522</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>0.7007501855493687</v>
+        <v>-6.790819024666016</v>
       </c>
       <c r="E1909" t="n">
-        <v>3.435962157574522</v>
+        <v>0.3708322806049411</v>
       </c>
       <c r="F1909" t="n">
-        <v>1.754061691333155</v>
+        <v>-0.3497538062941639</v>
       </c>
       <c r="G1909" t="n">
-        <v>4.208455522468415</v>
+        <v>2.877664031008597</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>4.043803538856293</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.156018507668522</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>0.7111039312128948</v>
+        <v>-6.642878983258417</v>
       </c>
       <c r="E1910" t="n">
-        <v>3.440103655839933</v>
+        <v>0.3101293744798133</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.754061691333155</v>
+        <v>-0.3294328903856064</v>
       </c>
       <c r="G1910" t="n">
-        <v>4.208455522468415</v>
+        <v>2.769977657865564</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>4.007036081554686</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.147304521415044</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>0.7640734534668837</v>
+        <v>-6.589909461004428</v>
       </c>
       <c r="E1911" t="n">
-        <v>3.45257747848805</v>
+        <v>0.3226031971279304</v>
       </c>
       <c r="F1911" t="n">
-        <v>1.807031213587144</v>
+        <v>-0.2764633681316175</v>
       </c>
       <c r="G1911" t="n">
-        <v>4.231523249567331</v>
+        <v>2.793045384964479</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>4.063112455146479</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.140343909319951</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>0.8116145259984449</v>
+        <v>-6.546361054233738</v>
       </c>
       <c r="E1912" t="n">
-        <v>3.464633295405581</v>
+        <v>0.3330619477411134</v>
       </c>
       <c r="F1912" t="n">
-        <v>1.807031213587144</v>
+        <v>-0.2764633681316175</v>
       </c>
       <c r="G1912" t="n">
-        <v>4.224562637472237</v>
+        <v>2.786084772869386</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>4.063112455146479</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.140343909319951</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>0.8116145259984449</v>
+        <v>-6.512997847754969</v>
       </c>
       <c r="E1913" t="n">
-        <v>3.464633295405581</v>
+        <v>0.3608695847137642</v>
       </c>
       <c r="F1913" t="n">
-        <v>1.807031213587144</v>
+        <v>-0.2764633681316175</v>
       </c>
       <c r="G1913" t="n">
-        <v>4.224562637472237</v>
+        <v>2.800547127250529</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>4.063112455146479</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.140343909319951</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>0.8116145259984449</v>
+        <v>-6.404738710632447</v>
       </c>
       <c r="E1914" t="n">
-        <v>3.464633295405581</v>
+        <v>0.3987053600219679</v>
       </c>
       <c r="F1914" t="n">
-        <v>1.807031213587144</v>
+        <v>-0.2764633681316175</v>
       </c>
       <c r="G1914" t="n">
-        <v>4.224562637472237</v>
+        <v>2.795079247709724</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>4.063112455146479</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.140343909319951</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>0.8116145259984449</v>
+        <v>-6.281447575815316</v>
       </c>
       <c r="E1915" t="n">
-        <v>3.464633295405581</v>
+        <v>0.445519907959397</v>
       </c>
       <c r="F1915" t="n">
-        <v>1.807031213587144</v>
+        <v>-0.153172233314487</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.224562637472237</v>
+        <v>2.866552022610579</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>4.063112455146479</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.140343909319951</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>0.8116145259984449</v>
+        <v>-6.260298376911873</v>
       </c>
       <c r="E1916" t="n">
-        <v>3.464633295405581</v>
+        <v>0.4616805657580993</v>
       </c>
       <c r="F1916" t="n">
-        <v>1.807031213587144</v>
+        <v>-0.1320230344110436</v>
       </c>
       <c r="G1916" t="n">
-        <v>4.224562637472237</v>
+        <v>2.88694252018997</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>4.063112455146479</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.140343909319951</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>0.8116145259984449</v>
+        <v>-6.016532934928429</v>
       </c>
       <c r="E1917" t="n">
-        <v>3.464633295405581</v>
+        <v>0.5549674508985278</v>
       </c>
       <c r="F1917" t="n">
-        <v>1.807031213587144</v>
+        <v>-0.1320230344110436</v>
       </c>
       <c r="G1917" t="n">
-        <v>4.224562637472237</v>
+        <v>2.882723228537021</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>4.063112455146479</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.140343909319951</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>0.8116145259984449</v>
+        <v>-5.914770114651134</v>
       </c>
       <c r="E1918" t="n">
-        <v>3.464633295405581</v>
+        <v>0.5977968929294621</v>
       </c>
       <c r="F1918" t="n">
-        <v>1.807031213587144</v>
+        <v>-0.1188039660186149</v>
       </c>
       <c r="G1918" t="n">
-        <v>4.224562637472237</v>
+        <v>2.892778983492494</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>4.063112455146479</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.140343909319951</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>0.8116145259984449</v>
+        <v>-5.664919720702059</v>
       </c>
       <c r="E1919" t="n">
-        <v>3.464633295405581</v>
+        <v>0.6904791254927938</v>
       </c>
       <c r="F1919" t="n">
-        <v>1.807031213587144</v>
+        <v>-0.1188039660186149</v>
       </c>
       <c r="G1919" t="n">
-        <v>4.224562637472237</v>
+        <v>2.885521058476196</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>4.063112455146479</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.140343909319951</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>0.8116145259984449</v>
+        <v>-5.489027628234627</v>
       </c>
       <c r="E1920" t="n">
-        <v>3.464633295405581</v>
+        <v>0.7644350860004154</v>
       </c>
       <c r="F1920" t="n">
-        <v>1.807031213587144</v>
+        <v>-0.1188039660186149</v>
       </c>
       <c r="G1920" t="n">
-        <v>4.224562637472237</v>
+        <v>2.889120181996845</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>4.063112455146479</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.140343909319951</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>0.8116145259984449</v>
+        <v>-5.317581165212164</v>
       </c>
       <c r="E1921" t="n">
-        <v>3.464633295405581</v>
+        <v>0.8463411772639544</v>
       </c>
       <c r="F1921" t="n">
-        <v>1.807031213587144</v>
+        <v>0.05264249700384821</v>
       </c>
       <c r="G1921" t="n">
-        <v>4.224562637472237</v>
+        <v>3.005315565864877</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>4.063112455146479</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.140343909319951</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>0.8116145259984449</v>
+        <v>-5.243291599473825</v>
       </c>
       <c r="E1922" t="n">
-        <v>3.464633295405581</v>
+        <v>0.875077481175587</v>
       </c>
       <c r="F1922" t="n">
-        <v>1.807031213587144</v>
+        <v>0.1269320627421875</v>
       </c>
       <c r="G1922" t="n">
-        <v>4.224562637472237</v>
+        <v>3.048909782924177</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>4.063112455146479</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.140343909319951</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>0.8116145259984449</v>
+        <v>-5.17965585723989</v>
       </c>
       <c r="E1923" t="n">
-        <v>3.464633295405581</v>
+        <v>0.9052265791234784</v>
       </c>
       <c r="F1923" t="n">
-        <v>1.807031213587144</v>
+        <v>0.190567804976122</v>
       </c>
       <c r="G1923" t="n">
-        <v>4.224562637472237</v>
+        <v>3.091786029318855</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>4.063112455146479</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.140343909319951</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>0.8116145259984449</v>
+        <v>-5.06822909791397</v>
       </c>
       <c r="E1924" t="n">
-        <v>3.464633295405581</v>
+        <v>0.930991541637642</v>
       </c>
       <c r="F1924" t="n">
-        <v>1.807031213587144</v>
+        <v>0.190567804976122</v>
       </c>
       <c r="G1924" t="n">
-        <v>4.224562637472237</v>
+        <v>3.072980288102651</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>4.063112455146479</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.140343909319951</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>0.8116145259984449</v>
+        <v>-5.078731720979259</v>
       </c>
       <c r="E1925" t="n">
-        <v>3.464633295405581</v>
+        <v>0.9285335690364036</v>
       </c>
       <c r="F1925" t="n">
-        <v>1.807031213587144</v>
+        <v>0.1800651819108331</v>
       </c>
       <c r="G1925" t="n">
-        <v>4.224562637472237</v>
+        <v>3.068421790888355</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>4.063112455146479</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.140343909319951</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>0.8116145259984449</v>
+        <v>-5.006489152808064</v>
       </c>
       <c r="E1926" t="n">
-        <v>3.464633295405581</v>
+        <v>0.9613599101397019</v>
       </c>
       <c r="F1926" t="n">
-        <v>1.807031213587144</v>
+        <v>0.1800651819108331</v>
       </c>
       <c r="G1926" t="n">
-        <v>4.224562637472237</v>
+        <v>3.072351104723175</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>4.063112455146479</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.140343909319951</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>0.8116145259984449</v>
+        <v>-4.988775465930199</v>
       </c>
       <c r="E1927" t="n">
-        <v>3.464633295405581</v>
+        <v>0.9691239688081881</v>
       </c>
       <c r="F1927" t="n">
-        <v>1.807031213587144</v>
+        <v>0.18324651080775</v>
       </c>
       <c r="G1927" t="n">
-        <v>4.224562637472237</v>
+        <v>3.074938485978665</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>4.063112455146479</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.140343909319951</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>0.8116145259984449</v>
+        <v>-4.879970580450472</v>
       </c>
       <c r="E1928" t="n">
-        <v>3.464633295405581</v>
+        <v>1.009643994220072</v>
       </c>
       <c r="F1928" t="n">
-        <v>1.807031213587144</v>
+        <v>0.18324651080775</v>
       </c>
       <c r="G1928" t="n">
-        <v>4.224562637472237</v>
+        <v>3.071936557198658</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>4.063112455146479</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.140343909319951</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>0.8116145259984449</v>
+        <v>-4.659949782413461</v>
       </c>
       <c r="E1929" t="n">
-        <v>3.464633295405581</v>
+        <v>1.099231350445491</v>
       </c>
       <c r="F1929" t="n">
-        <v>1.807031213587144</v>
+        <v>0.3244663558757302</v>
       </c>
       <c r="G1929" t="n">
-        <v>4.224562637472237</v>
+        <v>3.158247501250061</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>4.063112455146479</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.140343909319951</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>0.8116145259984449</v>
+        <v>-4.527082093350184</v>
       </c>
       <c r="E1930" t="n">
-        <v>3.464633295405581</v>
+        <v>1.168272608872625</v>
       </c>
       <c r="F1930" t="n">
-        <v>1.807031213587144</v>
+        <v>0.3244663558757302</v>
       </c>
       <c r="G1930" t="n">
-        <v>4.224562637472237</v>
+        <v>3.174141684051884</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>4.12058087848802</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.140343909319951</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>0.8055875014683731</v>
+        <v>-4.406909009985685</v>
       </c>
       <c r="E1931" t="n">
-        <v>3.462222485593553</v>
+        <v>1.217487686658726</v>
       </c>
       <c r="F1931" t="n">
-        <v>1.807031213587144</v>
+        <v>0.4446394392402291</v>
       </c>
       <c r="G1931" t="n">
-        <v>4.224562637472237</v>
+        <v>3.247391378510885</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.742626499572066</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.15043201188139</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>0.9391451149986102</v>
+        <v>-4.262236864885947</v>
       </c>
       <c r="E1932" t="n">
-        <v>3.525733633567087</v>
+        <v>1.285444647260061</v>
       </c>
       <c r="F1932" t="n">
-        <v>1.940588827117381</v>
+        <v>0.5893115843399666</v>
       </c>
       <c r="G1932" t="n">
-        <v>4.314785308151819</v>
+        <v>3.344282768132168</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.742626499572066</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.15043201188139</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>0.9391451149986102</v>
+        <v>-4.32211169224364</v>
       </c>
       <c r="E1933" t="n">
-        <v>3.525733633567087</v>
+        <v>1.24753220771841</v>
       </c>
       <c r="F1933" t="n">
-        <v>1.940588827117381</v>
+        <v>0.5294367569822744</v>
       </c>
       <c r="G1933" t="n">
-        <v>4.314785308151819</v>
+        <v>3.294395363118978</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.742626499572066</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.15043201188139</v>
+        <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>0.9391451149986102</v>
+        <v>-4.202291461332803</v>
       </c>
       <c r="E1934" t="n">
-        <v>3.525733633567087</v>
+        <v>1.310749469316953</v>
       </c>
       <c r="F1934" t="n">
-        <v>1.940588827117381</v>
+        <v>0.5294367569822744</v>
       </c>
       <c r="G1934" t="n">
-        <v>4.314785308151819</v>
+        <v>3.309684532353187</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.742626499572066</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.15043201188139</v>
+        <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>0.9391451149986102</v>
+        <v>-4.204761167794609</v>
       </c>
       <c r="E1935" t="n">
-        <v>3.525733633567087</v>
+        <v>1.217405786054673</v>
       </c>
       <c r="F1935" t="n">
-        <v>1.940588827117381</v>
+        <v>0.5269670505204682</v>
       </c>
       <c r="G1935" t="n">
-        <v>4.314785308151819</v>
+        <v>3.215846907798545</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.742626499572066</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.15043201188139</v>
+        <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>0.9391451149986102</v>
+        <v>-4.273131354118619</v>
       </c>
       <c r="E1936" t="n">
-        <v>3.525733633567087</v>
+        <v>1.10931957301037</v>
       </c>
       <c r="F1936" t="n">
-        <v>1.940588827117381</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1936" t="n">
-        <v>4.314785308151819</v>
+        <v>3.140674188705575</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.742626499572066</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.15043201188139</v>
+        <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>0.9391451149986102</v>
+        <v>-4.286919406965666</v>
       </c>
       <c r="E1937" t="n">
-        <v>3.525733633567087</v>
+        <v>1.094241060503442</v>
       </c>
       <c r="F1937" t="n">
-        <v>1.940588827117381</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1937" t="n">
-        <v>4.314785308151819</v>
+        <v>3.131110897337466</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.742626499572066</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
-        <v>3.15043201188139</v>
+        <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>0.9391451149986102</v>
+        <v>-4.342439482858255</v>
       </c>
       <c r="E1938" t="n">
-        <v>3.525733633567087</v>
+        <v>1.209063866838609</v>
       </c>
       <c r="F1938" t="n">
-        <v>1.940588827117381</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1938" t="n">
-        <v>4.314785308151819</v>
+        <v>3.268141734029669</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.742626499572066</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
-        <v>3.15043201188139</v>
+        <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>0.9391451149986102</v>
+        <v>-4.166965223065786</v>
       </c>
       <c r="E1939" t="n">
-        <v>3.525733633567087</v>
+        <v>1.283820802747385</v>
       </c>
       <c r="F1939" t="n">
-        <v>1.940588827117381</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1939" t="n">
-        <v>4.314785308151819</v>
+        <v>3.272708966021456</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.742626499572066</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
-        <v>3.15043201188139</v>
+        <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>0.9391451149986102</v>
+        <v>-4.277901475707035</v>
       </c>
       <c r="E1940" t="n">
-        <v>3.525733633567087</v>
+        <v>1.215188330452092</v>
       </c>
       <c r="F1940" t="n">
-        <v>1.940588827117381</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1940" t="n">
-        <v>4.314785308151819</v>
+        <v>3.248450994782663</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>4.230777191174315</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
-        <v>3.15043201188139</v>
+        <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>0.9407975304777006</v>
+        <v>-4.244237930234752</v>
       </c>
       <c r="E1941" t="n">
-        <v>3.526394599758723</v>
+        <v>1.157192062042455</v>
       </c>
       <c r="F1941" t="n">
-        <v>1.940588827117381</v>
+        <v>0.5699062950289651</v>
       </c>
       <c r="G1941" t="n">
-        <v>4.314785308151819</v>
+        <v>3.197187435467483</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>4.241910846327185</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
-        <v>3.160604398313523</v>
+        <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>1.000650149681424</v>
+        <v>-4.184385311031029</v>
       </c>
       <c r="E1942" t="n">
-        <v>3.560508033872345</v>
+        <v>1.191305496156077</v>
       </c>
       <c r="F1942" t="n">
-        <v>1.940588827117381</v>
+        <v>0.5699062950289651</v>
       </c>
       <c r="G1942" t="n">
-        <v>4.324957694583952</v>
+        <v>3.207359821899615</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>4.244516851805321</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
-        <v>3.155550668887383</v>
+        <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>1.086893612707801</v>
+        <v>-4.098141848004651</v>
       </c>
       <c r="E1943" t="n">
-        <v>3.589951689656756</v>
+        <v>1.220749151940488</v>
       </c>
       <c r="F1943" t="n">
-        <v>1.940588827117381</v>
+        <v>0.5699062950289651</v>
       </c>
       <c r="G1943" t="n">
-        <v>4.319903965157811</v>
+        <v>3.202306092473475</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>4.209594393379068</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
-        <v>3.147326444331909</v>
+        <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>1.041586793308821</v>
+        <v>-4.143448667403631</v>
       </c>
       <c r="E1944" t="n">
-        <v>3.56360473734169</v>
+        <v>1.194402199625421</v>
       </c>
       <c r="F1944" t="n">
-        <v>1.89977866410815</v>
+        <v>0.5290961320197343</v>
       </c>
       <c r="G1944" t="n">
-        <v>4.287193642796799</v>
+        <v>3.169595770112462</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>4.273630651107124</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
-        <v>3.14787831736501</v>
+        <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>1.012257448289408</v>
+        <v>-4.172481772105932</v>
       </c>
       <c r="E1945" t="n">
-        <v>3.552424872367026</v>
+        <v>1.183340830777603</v>
       </c>
       <c r="F1945" t="n">
-        <v>1.89977866410815</v>
+        <v>0.5290961320197343</v>
       </c>
       <c r="G1945" t="n">
-        <v>4.287745515829901</v>
+        <v>3.170147643145564</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>4.273630651107124</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
-        <v>3.14787831736501</v>
+        <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>1.012257448289408</v>
+        <v>-4.079671290655073</v>
       </c>
       <c r="E1946" t="n">
-        <v>3.552424872367026</v>
+        <v>1.149737715249312</v>
       </c>
       <c r="F1946" t="n">
-        <v>1.89977866410815</v>
+        <v>0.6219066134705936</v>
       </c>
       <c r="G1946" t="n">
-        <v>4.287745515829901</v>
+        <v>3.155106623907445</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>4.273630651107124</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
-        <v>3.14787831736501</v>
+        <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>1.012257448289408</v>
+        <v>-4.1240607599845</v>
       </c>
       <c r="E1947" t="n">
-        <v>3.552424872367026</v>
+        <v>1.133855403442142</v>
       </c>
       <c r="F1947" t="n">
-        <v>1.89977866410815</v>
+        <v>0.577517144141166</v>
       </c>
       <c r="G1947" t="n">
-        <v>4.287745515829901</v>
+        <v>3.130346418234389</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>4.273630651107124</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
-        <v>3.14787831736501</v>
+        <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>1.012257448289408</v>
+        <v>-4.240602365089843</v>
       </c>
       <c r="E1948" t="n">
-        <v>3.552424872367026</v>
+        <v>1.082314469911728</v>
       </c>
       <c r="F1948" t="n">
-        <v>1.89977866410815</v>
+        <v>0.4609755390358232</v>
       </c>
       <c r="G1948" t="n">
-        <v>4.287745515829901</v>
+        <v>3.055497163682907</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>4.273630651107124</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
-        <v>3.14787831736501</v>
+        <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>1.012257448289408</v>
+        <v>-4.12822536390717</v>
       </c>
       <c r="E1949" t="n">
-        <v>3.552424872367026</v>
+        <v>1.132756566215464</v>
       </c>
       <c r="F1949" t="n">
-        <v>1.89977866410815</v>
+        <v>0.4609755390358232</v>
       </c>
       <c r="G1949" t="n">
-        <v>4.287745515829901</v>
+        <v>3.060988459513574</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>4.273630651107124</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
-        <v>3.14787831736501</v>
+        <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>1.012257448289408</v>
+        <v>-4.156005761808522</v>
       </c>
       <c r="E1950" t="n">
-        <v>3.552424872367026</v>
+        <v>1.133141608823462</v>
       </c>
       <c r="F1950" t="n">
-        <v>1.89977866410815</v>
+        <v>0.4331951411344701</v>
       </c>
       <c r="G1950" t="n">
-        <v>4.287745515829901</v>
+        <v>3.055817422541301</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>4.273630651107124</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
-        <v>3.14787831736501</v>
+        <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>1.012257448289408</v>
+        <v>-4.274386434538661</v>
       </c>
       <c r="E1951" t="n">
-        <v>3.552424872367026</v>
+        <v>0.9241450597320604</v>
       </c>
       <c r="F1951" t="n">
-        <v>1.89977866410815</v>
+        <v>0.3659772889834939</v>
       </c>
       <c r="G1951" t="n">
-        <v>4.287745515829901</v>
+        <v>2.853842431251369</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>4.273630651107124</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
-        <v>3.14787831736501</v>
+        <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>1.012257448289408</v>
+        <v>-4.383000512981992</v>
       </c>
       <c r="E1952" t="n">
-        <v>3.552424872367026</v>
+        <v>1.000849089073933</v>
       </c>
       <c r="F1952" t="n">
-        <v>1.89977866410815</v>
+        <v>0.3659772889834939</v>
       </c>
       <c r="G1952" t="n">
-        <v>4.287745515829901</v>
+        <v>2.973992091970574</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>4.273630651107124</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
-        <v>3.14787831736501</v>
+        <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>1.012257448289408</v>
+        <v>-4.347591474733849</v>
       </c>
       <c r="E1953" t="n">
-        <v>3.552424872367026</v>
+        <v>1.029525730475514</v>
       </c>
       <c r="F1953" t="n">
-        <v>1.89977866410815</v>
+        <v>0.3659772889834939</v>
       </c>
       <c r="G1953" t="n">
-        <v>4.287745515829901</v>
+        <v>2.988505118072897</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>4.273630651107124</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
-        <v>3.14787831736501</v>
+        <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>1.012257448289408</v>
+        <v>-4.309207812175698</v>
       </c>
       <c r="E1954" t="n">
-        <v>3.552424872367026</v>
+        <v>1.042298636841143</v>
       </c>
       <c r="F1954" t="n">
-        <v>1.89977866410815</v>
+        <v>0.4043609515416451</v>
       </c>
       <c r="G1954" t="n">
-        <v>4.287745515829901</v>
+        <v>3.008954756950156</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>4.273630651107124</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
-        <v>3.14787831736501</v>
+        <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>1.012257448289408</v>
+        <v>-4.132091482140532</v>
       </c>
       <c r="E1955" t="n">
-        <v>3.552424872367026</v>
+        <v>1.109874197700511</v>
       </c>
       <c r="F1955" t="n">
-        <v>1.89977866410815</v>
+        <v>0.4043609515416451</v>
       </c>
       <c r="G1955" t="n">
-        <v>4.287745515829901</v>
+        <v>3.005683785795458</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>4.273630651107124</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
-        <v>3.14787831736501</v>
+        <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>1.012257448289408</v>
+        <v>-4.177183726974078</v>
       </c>
       <c r="E1956" t="n">
-        <v>3.552424872367026</v>
+        <v>1.092520691529006</v>
       </c>
       <c r="F1956" t="n">
-        <v>1.89977866410815</v>
+        <v>0.3424649083722553</v>
       </c>
       <c r="G1956" t="n">
-        <v>4.287745515829901</v>
+        <v>2.969229551655738</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>4.273630651107124</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
-        <v>3.14787831736501</v>
+        <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>1.012257448289408</v>
+        <v>-3.99780830573531</v>
       </c>
       <c r="E1957" t="n">
-        <v>3.552424872367026</v>
+        <v>1.158057835330927</v>
       </c>
       <c r="F1957" t="n">
-        <v>1.89977866410815</v>
+        <v>0.499241666542974</v>
       </c>
       <c r="G1957" t="n">
-        <v>4.287745515829901</v>
+        <v>3.057082581864583</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>4.273630651107124</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
-        <v>3.14787831736501</v>
+        <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>1.012257448289408</v>
+        <v>-4.042822519255916</v>
       </c>
       <c r="E1958" t="n">
-        <v>3.552424872367026</v>
+        <v>1.120859605254275</v>
       </c>
       <c r="F1958" t="n">
-        <v>1.89977866410815</v>
+        <v>0.4688927712283694</v>
       </c>
       <c r="G1958" t="n">
-        <v>4.287745515829901</v>
+        <v>3.01968070000741</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>4.273630651107124</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
-        <v>3.14787831736501</v>
+        <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>1.012257448289408</v>
+        <v>-4.309827029528351</v>
       </c>
       <c r="E1959" t="n">
-        <v>3.552424872367026</v>
+        <v>1.019749363484246</v>
       </c>
       <c r="F1959" t="n">
-        <v>1.89977866410815</v>
+        <v>0.2745297331854208</v>
       </c>
       <c r="G1959" t="n">
-        <v>4.287745515829901</v>
+        <v>2.908754439520587</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>4.161544549677852</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
-        <v>3.14787831736501</v>
+        <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>1.011629153911424</v>
+        <v>-4.411024810965523</v>
       </c>
       <c r="E1960" t="n">
-        <v>3.552173554615833</v>
+        <v>0.9784741728058788</v>
       </c>
       <c r="F1960" t="n">
-        <v>1.89977866410815</v>
+        <v>0.2061209196401016</v>
       </c>
       <c r="G1960" t="n">
-        <v>4.287745515829901</v>
+        <v>2.866913073289897</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>4.202348812479487</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
-        <v>3.145478278919327</v>
+        <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>1.018897699016924</v>
+        <v>-4.404513844351211</v>
       </c>
       <c r="E1961" t="n">
-        <v>3.552680934212349</v>
+        <v>0.9786785210059206</v>
       </c>
       <c r="F1961" t="n">
-        <v>1.89977866410815</v>
+        <v>0.2061209196401016</v>
       </c>
       <c r="G1961" t="n">
-        <v>4.285345477384217</v>
+        <v>2.864513034844213</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>4.202348812479487</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
-        <v>3.145478278919327</v>
+        <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>1.018897699016924</v>
+        <v>-4.385475716643914</v>
       </c>
       <c r="E1962" t="n">
-        <v>3.552680934212349</v>
+        <v>0.9828184912970845</v>
       </c>
       <c r="F1962" t="n">
-        <v>1.89977866410815</v>
+        <v>0.1479373083089071</v>
       </c>
       <c r="G1962" t="n">
-        <v>4.285345477384217</v>
+        <v>2.826127587253742</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>4.202348812479487</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>3.145478278919327</v>
+        <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>1.018897699016924</v>
+        <v>-4.416602347794532</v>
       </c>
       <c r="E1963" t="n">
-        <v>3.552680934212349</v>
+        <v>1.089662240471027</v>
       </c>
       <c r="F1963" t="n">
-        <v>1.89977866410815</v>
+        <v>0.1479373083089071</v>
       </c>
       <c r="G1963" t="n">
-        <v>4.285345477384217</v>
+        <v>2.945421988887932</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>4.202348812479487</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>3.145478278919327</v>
+        <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>1.018897699016924</v>
+        <v>-4.43046910912845</v>
       </c>
       <c r="E1964" t="n">
-        <v>3.552680934212349</v>
+        <v>1.084948864923594</v>
       </c>
       <c r="F1964" t="n">
-        <v>1.89977866410815</v>
+        <v>0.1100793915750841</v>
       </c>
       <c r="G1964" t="n">
-        <v>4.285345477384217</v>
+        <v>2.923540567833772</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>4.202348812479487</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.145478278919327</v>
+        <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>1.018897699016924</v>
+        <v>-4.38566493758852</v>
       </c>
       <c r="E1965" t="n">
-        <v>3.552680934212349</v>
+        <v>1.108879063936492</v>
       </c>
       <c r="F1965" t="n">
-        <v>1.89977866410815</v>
+        <v>0.1100793915750841</v>
       </c>
       <c r="G1965" t="n">
-        <v>4.285345477384217</v>
+        <v>2.929549098230698</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>4.202348812479487</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.145478278919327</v>
+        <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>1.018897699016924</v>
+        <v>-4.237921967353517</v>
       </c>
       <c r="E1966" t="n">
-        <v>3.552680934212349</v>
+        <v>1.065926473307692</v>
       </c>
       <c r="F1966" t="n">
-        <v>1.89977866410815</v>
+        <v>0.2778867488099673</v>
       </c>
       <c r="G1966" t="n">
-        <v>4.285345477384217</v>
+        <v>2.928183733848827</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>4.202348812479487</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.145478278919327</v>
+        <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>1.018897699016924</v>
+        <v>-4.321743188628216</v>
       </c>
       <c r="E1967" t="n">
-        <v>3.552680934212349</v>
+        <v>1.035191606329294</v>
       </c>
       <c r="F1967" t="n">
-        <v>1.89977866410815</v>
+        <v>0.2778867488099673</v>
       </c>
       <c r="G1967" t="n">
-        <v>4.285345477384217</v>
+        <v>2.930977355380308</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>4.202348812479487</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.145478278919327</v>
+        <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>1.018897699016924</v>
+        <v>-4.315590482575431</v>
       </c>
       <c r="E1968" t="n">
-        <v>3.552680934212349</v>
+        <v>1.038315037142066</v>
       </c>
       <c r="F1968" t="n">
-        <v>1.89977866410815</v>
+        <v>0.2840394548627516</v>
       </c>
       <c r="G1968" t="n">
-        <v>4.285345477384217</v>
+        <v>2.935331327403637</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>4.202348812479487</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.145478278919327</v>
+        <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>1.018897699016924</v>
+        <v>-4.332399780725933</v>
       </c>
       <c r="E1969" t="n">
-        <v>3.552680934212349</v>
+        <v>1.030671794621975</v>
       </c>
       <c r="F1969" t="n">
-        <v>1.89977866410815</v>
+        <v>0.2672301567122499</v>
       </c>
       <c r="G1969" t="n">
-        <v>4.285345477384217</v>
+        <v>2.924326225253446</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>4.202348812479487</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.145478278919327</v>
+        <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>1.018897699016924</v>
+        <v>-4.270101781949811</v>
       </c>
       <c r="E1970" t="n">
-        <v>3.552680934212349</v>
+        <v>1.121926547929245</v>
       </c>
       <c r="F1970" t="n">
-        <v>1.89977866410815</v>
+        <v>0.2672301567122499</v>
       </c>
       <c r="G1970" t="n">
-        <v>4.285345477384217</v>
+        <v>2.990661779050267</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>4.202348812479487</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>3.145478278919327</v>
+        <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>1.018897699016924</v>
+        <v>-4.068311584284653</v>
       </c>
       <c r="E1971" t="n">
-        <v>3.552680934212349</v>
+        <v>1.004934628709436</v>
       </c>
       <c r="F1971" t="n">
-        <v>1.89977866410815</v>
+        <v>0.4652483488814043</v>
       </c>
       <c r="G1971" t="n">
-        <v>4.285345477384217</v>
+        <v>2.911764696065887</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>4.301006129572143</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
-        <v>3.145478278919327</v>
+        <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>1.015773283084842</v>
+        <v>-4.119198296970848</v>
       </c>
       <c r="E1972" t="n">
-        <v>3.551431167839517</v>
+        <v>1.054870175957133</v>
       </c>
       <c r="F1972" t="n">
-        <v>1.89977866410815</v>
+        <v>0.4143616361952098</v>
       </c>
       <c r="G1972" t="n">
-        <v>4.285345477384217</v>
+        <v>2.951522900776345</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>4.309071084658199</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
-        <v>3.160106015035371</v>
+        <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>0.9189543247206278</v>
+        <v>-4.216938841595822</v>
       </c>
       <c r="E1973" t="n">
-        <v>3.527331320609874</v>
+        <v>1.030401694223187</v>
       </c>
       <c r="F1973" t="n">
-        <v>1.88224677439211</v>
+        <v>0.3984723580622296</v>
       </c>
       <c r="G1973" t="n">
-        <v>4.289454079670636</v>
+        <v>2.956617070012601</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>4.309071084658199</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
-        <v>3.160106015035371</v>
+        <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>0.9189543247206278</v>
+        <v>-4.277148139601107</v>
       </c>
       <c r="E1974" t="n">
-        <v>3.527331320609874</v>
+        <v>1.004853955845745</v>
       </c>
       <c r="F1974" t="n">
-        <v>1.88224677439211</v>
+        <v>0.3382630600569451</v>
       </c>
       <c r="G1974" t="n">
-        <v>4.289454079670636</v>
+        <v>2.919027472034102</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>4.309071084658199</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
-        <v>3.160106015035371</v>
+        <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>0.9189543247206278</v>
+        <v>-4.20072609316918</v>
       </c>
       <c r="E1975" t="n">
-        <v>3.527331320609874</v>
+        <v>1.033914392458444</v>
       </c>
       <c r="F1975" t="n">
-        <v>1.88224677439211</v>
+        <v>0.3382630600569451</v>
       </c>
       <c r="G1975" t="n">
-        <v>4.289454079670636</v>
+        <v>2.91751909007403</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>4.309071084658199</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
-        <v>3.160106015035371</v>
+        <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>0.9189543247206278</v>
+        <v>-4.156352961530612</v>
       </c>
       <c r="E1976" t="n">
-        <v>3.527331320609874</v>
+        <v>1.051526512549307</v>
       </c>
       <c r="F1976" t="n">
-        <v>1.88224677439211</v>
+        <v>0.3826361916955137</v>
       </c>
       <c r="G1976" t="n">
-        <v>4.289454079670636</v>
+        <v>2.944005836492608</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>4.281131852972788</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
-        <v>3.160106015035371</v>
+        <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>0.9269082950154001</v>
+        <v>-4.178833312389497</v>
       </c>
       <c r="E1977" t="n">
-        <v>3.530512908727784</v>
+        <v>1.036928166344344</v>
       </c>
       <c r="F1977" t="n">
-        <v>1.88224677439211</v>
+        <v>0.3826361916955137</v>
       </c>
       <c r="G1977" t="n">
-        <v>4.289454079670636</v>
+        <v>2.938399630631198</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>4.292580884057146</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
-        <v>3.166487772063175</v>
+        <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>0.9745640255764557</v>
+        <v>-4.131177581828441</v>
       </c>
       <c r="E1978" t="n">
-        <v>3.55595695798001</v>
+        <v>1.062372215596571</v>
       </c>
       <c r="F1978" t="n">
-        <v>1.929902504953166</v>
+        <v>0.4302919222565693</v>
       </c>
       <c r="G1978" t="n">
-        <v>4.324429275035075</v>
+        <v>2.973374825995637</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>4.16501288659792</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>3.1713801454379</v>
+        <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>1.081595459914701</v>
+        <v>-4.030659423329686</v>
       </c>
       <c r="E1979" t="n">
-        <v>3.603661905090033</v>
+        <v>1.107471852370798</v>
       </c>
       <c r="F1979" t="n">
-        <v>2.036933939291411</v>
+        <v>0.5308100807553239</v>
       </c>
       <c r="G1979" t="n">
-        <v>4.393540509012747</v>
+        <v>3.038578094469614</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>4.16501288659792</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
-        <v>3.1713801454379</v>
+        <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>1.081595459914701</v>
+        <v>-4.091326013732075</v>
       </c>
       <c r="E1980" t="n">
-        <v>3.603661905090033</v>
+        <v>1.069959888685714</v>
       </c>
       <c r="F1980" t="n">
-        <v>2.036933939291411</v>
+        <v>0.4491117640367902</v>
       </c>
       <c r="G1980" t="n">
-        <v>4.393540509012747</v>
+        <v>2.976313776914366</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>4.16501288659792</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>3.1713801454379</v>
+        <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>1.081595459914701</v>
+        <v>-4.046487612123677</v>
       </c>
       <c r="E1981" t="n">
-        <v>3.603661905090033</v>
+        <v>1.091992951939702</v>
       </c>
       <c r="F1981" t="n">
-        <v>2.036933939291411</v>
+        <v>0.4536551969816597</v>
       </c>
       <c r="G1981" t="n">
-        <v>4.393540509012747</v>
+        <v>2.983137539291916</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>4.16501288659792</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>3.1713801454379</v>
+        <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>1.081595459914701</v>
+        <v>-4.065986068365685</v>
       </c>
       <c r="E1982" t="n">
-        <v>3.603661905090033</v>
+        <v>1.088354509073977</v>
       </c>
       <c r="F1982" t="n">
-        <v>2.036933939291411</v>
+        <v>0.4055705557017554</v>
       </c>
       <c r="G1982" t="n">
-        <v>4.393540509012747</v>
+        <v>2.958447694155052</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>4.16501288659792</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>3.1713801454379</v>
+        <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>1.081595459914701</v>
+        <v>-4.021783231279785</v>
       </c>
       <c r="E1983" t="n">
-        <v>3.603661905090033</v>
+        <v>1.111915246436174</v>
       </c>
       <c r="F1983" t="n">
-        <v>2.036933939291411</v>
+        <v>0.4497733927876558</v>
       </c>
       <c r="G1983" t="n">
-        <v>4.393540509012747</v>
+        <v>2.990848998934429</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>4.16501288659792</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>3.1713801454379</v>
+        <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>1.081595459914701</v>
+        <v>-4.058762258943228</v>
       </c>
       <c r="E1984" t="n">
-        <v>3.603661905090033</v>
+        <v>1.095533635840044</v>
       </c>
       <c r="F1984" t="n">
-        <v>2.036933939291411</v>
+        <v>0.4867472945789864</v>
       </c>
       <c r="G1984" t="n">
-        <v>4.393540509012747</v>
+        <v>3.011443340478475</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>4.16501288659792</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>3.1713801454379</v>
+        <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>1.081595459914701</v>
+        <v>-3.900470841403955</v>
       </c>
       <c r="E1985" t="n">
-        <v>3.603661905090033</v>
+        <v>1.210097968038793</v>
       </c>
       <c r="F1985" t="n">
-        <v>2.036933939291411</v>
+        <v>0.4867472945789864</v>
       </c>
       <c r="G1985" t="n">
-        <v>4.393540509012747</v>
+        <v>3.062691105661515</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>4.16501288659792</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>3.1713801454379</v>
+        <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>1.081595459914701</v>
+        <v>-3.692828837769479</v>
       </c>
       <c r="E1986" t="n">
-        <v>3.603661905090033</v>
+        <v>1.291595474086837</v>
       </c>
       <c r="F1986" t="n">
-        <v>2.036933939291411</v>
+        <v>0.6943892982134625</v>
       </c>
       <c r="G1986" t="n">
-        <v>4.393540509012747</v>
+        <v>3.185717012436454</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>4.16501288659792</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>3.1713801454379</v>
+        <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>1.081595459914701</v>
+        <v>-3.641796745046951</v>
       </c>
       <c r="E1987" t="n">
-        <v>3.603661905090033</v>
+        <v>1.306956539414118</v>
       </c>
       <c r="F1987" t="n">
-        <v>2.036933939291411</v>
+        <v>0.7454213909359905</v>
       </c>
       <c r="G1987" t="n">
-        <v>4.393540509012747</v>
+        <v>3.21128449630824</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>4.16501288659792</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>3.1713801454379</v>
+        <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>1.081595459914701</v>
+        <v>-3.576572563919745</v>
       </c>
       <c r="E1988" t="n">
-        <v>3.603661905090033</v>
+        <v>1.350233615957705</v>
       </c>
       <c r="F1988" t="n">
-        <v>2.036933939291411</v>
+        <v>0.8106455720631961</v>
       </c>
       <c r="G1988" t="n">
-        <v>4.393540509012747</v>
+        <v>3.267606409077268</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>4.16501288659792</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>3.1713801454379</v>
+        <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>1.081595459914701</v>
+        <v>-3.539145543848611</v>
       </c>
       <c r="E1989" t="n">
-        <v>3.603661905090033</v>
+        <v>1.361165396285439</v>
       </c>
       <c r="F1989" t="n">
-        <v>2.036933939291411</v>
+        <v>0.8158971100923778</v>
       </c>
       <c r="G1989" t="n">
-        <v>4.393540509012747</v>
+        <v>3.266718304194058</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>4.16501288659792</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
-        <v>3.1713801454379</v>
+        <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>1.081595459914701</v>
+        <v>-3.55925719988332</v>
       </c>
       <c r="E1990" t="n">
-        <v>3.603661905090033</v>
+        <v>1.354377526202796</v>
       </c>
       <c r="F1990" t="n">
-        <v>2.036933939291411</v>
+        <v>0.826924455089797</v>
       </c>
       <c r="G1990" t="n">
-        <v>4.393540509012747</v>
+        <v>3.27459150352375</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>4.16501288659792</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.1713801454379</v>
+        <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>1.081595459914701</v>
+        <v>-3.505512385456115</v>
       </c>
       <c r="E1991" t="n">
-        <v>3.603661905090033</v>
+        <v>1.536433222994889</v>
       </c>
       <c r="F1991" t="n">
-        <v>2.036933939291411</v>
+        <v>0.8369877645302589</v>
       </c>
       <c r="G1991" t="n">
-        <v>4.393540509012747</v>
+        <v>3.441187260209237</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>4.16501288659792</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.1713801454379</v>
+        <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>1.081595459914701</v>
+        <v>-3.430730124431102</v>
       </c>
       <c r="E1992" t="n">
-        <v>3.603661905090033</v>
+        <v>1.686459036622711</v>
       </c>
       <c r="F1992" t="n">
-        <v>2.036933939291411</v>
+        <v>0.9117700255552715</v>
       </c>
       <c r="G1992" t="n">
-        <v>4.393540509012747</v>
+        <v>3.606169526042062</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>4.288678101227712</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.1713801454379</v>
+        <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>1.08429674140647</v>
+        <v>-3.404646040167294</v>
       </c>
       <c r="E1993" t="n">
-        <v>3.604742417686741</v>
+        <v>1.688600646342093</v>
       </c>
       <c r="F1993" t="n">
-        <v>2.036933939291411</v>
+        <v>0.9117700255552715</v>
       </c>
       <c r="G1993" t="n">
-        <v>4.393540509012747</v>
+        <v>3.597877502055921</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>4.197044094829781</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.16957334102168</v>
+        <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>1.164556448233739</v>
+        <v>-3.326514859318348</v>
       </c>
       <c r="E1994" t="n">
-        <v>3.635039496001428</v>
+        <v>1.718046314265451</v>
       </c>
       <c r="F1994" t="n">
-        <v>2.111322140003834</v>
+        <v>0.9859468364389561</v>
       </c>
       <c r="G1994" t="n">
-        <v>4.43636662502398</v>
+        <v>3.640576784169911</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>4.197044094829781</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.16957334102168</v>
+        <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>1.164556448233739</v>
+        <v>-3.317622397925065</v>
       </c>
       <c r="E1995" t="n">
-        <v>3.635039496001428</v>
+        <v>1.739157704549556</v>
       </c>
       <c r="F1995" t="n">
-        <v>2.111322140003834</v>
+        <v>0.9859468364389561</v>
       </c>
       <c r="G1995" t="n">
-        <v>4.43636662502398</v>
+        <v>3.658131189896703</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>4.197044094829781</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.16957334102168</v>
+        <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>1.164556448233739</v>
+        <v>-3.486098514894942</v>
       </c>
       <c r="E1996" t="n">
-        <v>3.635039496001428</v>
+        <v>1.663622305166189</v>
       </c>
       <c r="F1996" t="n">
-        <v>2.111322140003834</v>
+        <v>0.9579990007223753</v>
       </c>
       <c r="G1996" t="n">
-        <v>4.43636662502398</v>
+        <v>3.633217535871339</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>4.197044094829781</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.16957334102168</v>
+        <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>1.164556448233739</v>
+        <v>-2.788298986033359</v>
       </c>
       <c r="E1997" t="n">
-        <v>3.635039496001428</v>
+        <v>1.924011813898684</v>
       </c>
       <c r="F1997" t="n">
-        <v>2.111322140003834</v>
+        <v>0.8876509413519647</v>
       </c>
       <c r="G1997" t="n">
-        <v>4.43636662502398</v>
+        <v>3.572278397436954</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>4.197044094829781</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.16957334102168</v>
+        <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>1.164556448233739</v>
+        <v>-2.765577882350207</v>
       </c>
       <c r="E1998" t="n">
-        <v>3.635039496001428</v>
+        <v>1.92376427786885</v>
       </c>
       <c r="F1998" t="n">
-        <v>2.111322140003834</v>
+        <v>0.8876509413519647</v>
       </c>
       <c r="G1998" t="n">
-        <v>4.43636662502398</v>
+        <v>3.562942419933858</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>4.197044094829781</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.16957334102168</v>
+        <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>1.164556448233739</v>
+        <v>-2.894779695644249</v>
       </c>
       <c r="E1999" t="n">
-        <v>3.635039496001428</v>
+        <v>2.030989678402402</v>
       </c>
       <c r="F1999" t="n">
-        <v>2.111322140003834</v>
+        <v>0.7584491280579224</v>
       </c>
       <c r="G1999" t="n">
-        <v>4.43636662502398</v>
+        <v>3.644327457808602</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>4.197044094829781</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.16957334102168</v>
+        <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>1.164556448233739</v>
+        <v>-3.049560702422505</v>
       </c>
       <c r="E2000" t="n">
-        <v>3.635039496001428</v>
+        <v>2.006155098184746</v>
       </c>
       <c r="F2000" t="n">
-        <v>2.111322140003834</v>
+        <v>0.7250814540034463</v>
       </c>
       <c r="G2000" t="n">
-        <v>4.43636662502398</v>
+        <v>3.661384675869563</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>4.197044094829781</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.16957334102168</v>
+        <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>1.164556448233739</v>
+        <v>-3.042506012207331</v>
       </c>
       <c r="E2001" t="n">
-        <v>3.635039496001428</v>
+        <v>2.00565233026036</v>
       </c>
       <c r="F2001" t="n">
-        <v>2.111322140003834</v>
+        <v>0.7321361442186201</v>
       </c>
       <c r="G2001" t="n">
-        <v>4.43636662502398</v>
+        <v>3.662292845988212</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>4.197044094829781</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.16957334102168</v>
+        <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>1.164556448233739</v>
+        <v>-3.015554787880843</v>
       </c>
       <c r="E2002" t="n">
-        <v>3.635039496001428</v>
+        <v>2.026438973635697</v>
       </c>
       <c r="F2002" t="n">
-        <v>2.111322140003834</v>
+        <v>0.7470164902463392</v>
       </c>
       <c r="G2002" t="n">
-        <v>4.43636662502398</v>
+        <v>3.681227207249585</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>4.197044094829781</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.16957334102168</v>
+        <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>1.164556448233739</v>
+        <v>-3.151507795937159</v>
       </c>
       <c r="E2003" t="n">
-        <v>3.635039496001428</v>
+        <v>2.15616090255813</v>
       </c>
       <c r="F2003" t="n">
-        <v>2.111322140003834</v>
+        <v>0.7470164902463392</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.43636662502398</v>
+        <v>3.865330339394545</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>4.222660019922719</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.16957334102168</v>
+        <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>1.166569951599757</v>
+        <v>-3.173915913742031</v>
       </c>
       <c r="E2004" t="n">
-        <v>3.635844897347835</v>
+        <v>2.139314350339175</v>
       </c>
       <c r="F2004" t="n">
-        <v>2.111322140003834</v>
+        <v>0.7470164902463392</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.43636662502398</v>
+        <v>3.857447034297538</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>4.193566768037636</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.171627340571317</v>
+        <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>1.021360275791089</v>
+        <v>-3.321921681221431</v>
       </c>
       <c r="E2005" t="n">
-        <v>3.579815026574005</v>
+        <v>2.082166042897052</v>
       </c>
       <c r="F2005" t="n">
-        <v>2.025813597195189</v>
+        <v>0.6602894813827977</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.387115498888431</v>
+        <v>3.807464828529051</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.913967520808999</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.171627340571317</v>
+        <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>1.021360275791089</v>
+        <v>-3.331362607109961</v>
       </c>
       <c r="E2006" t="n">
-        <v>3.579815026574005</v>
+        <v>2.134643390263487</v>
       </c>
       <c r="F2006" t="n">
-        <v>2.025813597195189</v>
+        <v>0.7827165989261892</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.387115498888431</v>
+        <v>3.937174816776933</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.913967520808999</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.171627340571317</v>
+        <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>1.021360275791089</v>
+        <v>-3.383636214445602</v>
       </c>
       <c r="E2007" t="n">
-        <v>3.579815026574005</v>
+        <v>2.116625041874532</v>
       </c>
       <c r="F2007" t="n">
-        <v>2.025813597195189</v>
+        <v>0.7304429915905479</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.387115498888431</v>
+        <v>3.908701746920849</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.913967520808999</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.171627340571317</v>
+        <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>1.021360275791089</v>
+        <v>-3.459966192046508</v>
       </c>
       <c r="E2008" t="n">
-        <v>3.579815026574005</v>
+        <v>2.084204863727945</v>
       </c>
       <c r="F2008" t="n">
-        <v>2.025813597195189</v>
+        <v>0.7304429915905479</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.387115498888431</v>
+        <v>3.906813559814624</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.913967520808999</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.171627340571317</v>
+        <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>1.021360275791089</v>
+        <v>-3.662219912370861</v>
       </c>
       <c r="E2009" t="n">
-        <v>3.579815026574005</v>
+        <v>1.998123605201066</v>
       </c>
       <c r="F2009" t="n">
-        <v>2.025813597195189</v>
+        <v>0.5281892712661944</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.387115498888431</v>
+        <v>3.780281557222875</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.913967520808999</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.171627340571317</v>
+        <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>1.021360275791089</v>
+        <v>-3.823788337898117</v>
       </c>
       <c r="E2010" t="n">
-        <v>3.579815026574005</v>
+        <v>1.931930245200316</v>
       </c>
       <c r="F2010" t="n">
-        <v>2.025813597195189</v>
+        <v>0.4014063474683151</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.387115498888431</v>
+        <v>3.702645813154299</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.913967520808999</v>
+        <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.171627340571317</v>
+        <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>1.021360275791089</v>
+        <v>-3.95608962999567</v>
       </c>
       <c r="E2011" t="n">
-        <v>3.579815026574005</v>
+        <v>1.892083135227213</v>
       </c>
       <c r="F2011" t="n">
-        <v>2.025813597195189</v>
+        <v>0.4014063474683151</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.387115498888431</v>
+        <v>3.715719220020218</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>4.349971443633434</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.171627340571317</v>
+        <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>1.019798632976229</v>
+        <v>-4.141957940834899</v>
       </c>
       <c r="E2012" t="n">
-        <v>3.579190369448061</v>
+        <v>1.809741007674461</v>
       </c>
       <c r="F2012" t="n">
-        <v>2.025813597195189</v>
+        <v>0.2428407541483674</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.387115498888431</v>
+        <v>3.612585060811189</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>4.409480289874755</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.170151381698319</v>
+        <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>0.9862832614152426</v>
+        <v>-4.169858727944372</v>
       </c>
       <c r="E2013" t="n">
-        <v>3.564308261950669</v>
+        <v>1.797104733957674</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.986737464424265</v>
+        <v>0.2082438300054326</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.362193860352878</v>
+        <v>3.59035094745243</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>4.409480289874755</v>
+        <v>3.684895778787383</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.170151381698319</v>
+        <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>0.9862832614152426</v>
+        <v>-4.292384830647266</v>
       </c>
       <c r="E2014" t="n">
-        <v>3.564308261950669</v>
+        <v>1.744858736853716</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.986737464424265</v>
+        <v>0.08571772730253868</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.362193860352878</v>
+        <v>3.513599729807892</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>4.409480289874755</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.170151381698319</v>
+        <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>0.9862832614152426</v>
+        <v>-4.522899326832855</v>
       </c>
       <c r="E2015" t="n">
-        <v>3.564308261950669</v>
+        <v>1.719358897969984</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.14479676888305</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.362193860352878</v>
+        <v>3.441996991687043</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>4.409480289874755</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.170151381698319</v>
+        <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>0.9862832614152426</v>
+        <v>-4.779620144827678</v>
       </c>
       <c r="E2016" t="n">
-        <v>3.564308261950669</v>
+        <v>1.756982289773901</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.2532113430268649</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.362193860352878</v>
+        <v>3.517259966202601</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>4.409480289874755</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.170151381698319</v>
+        <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>0.9862832614152426</v>
+        <v>-4.933606562603819</v>
       </c>
       <c r="E2017" t="n">
-        <v>3.564308261950669</v>
+        <v>1.764367991809085</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.2532113430268649</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.362193860352878</v>
+        <v>3.586240235348241</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>4.409480289874755</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.170151381698319</v>
+        <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>0.9862832614152426</v>
+        <v>-4.883084658776153</v>
       </c>
       <c r="E2018" t="n">
-        <v>3.564308261950669</v>
+        <v>1.770627955460272</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.2532113430268649</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.362193860352878</v>
+        <v>3.572291437468362</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>4.409480289874755</v>
+        <v>3.65633273360975</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.170151381698319</v>
+        <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.135559812783877</v>
       </c>
       <c r="E2019" t="n">
-        <v>3.564308261950669</v>
+        <v>1.681508382912596</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.2532113430268649</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.362193860352878</v>
+        <v>3.584161926523776</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>4.409480289874755</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.170151381698319</v>
+        <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.428455569263289</v>
       </c>
       <c r="E2020" t="n">
-        <v>3.564308261950669</v>
+        <v>1.565560614839775</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.2532113430268649</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.362193860352878</v>
+        <v>3.58537246104272</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>4.409480289874755</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.170151381698319</v>
+        <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.585999640992731</v>
       </c>
       <c r="E2021" t="n">
-        <v>3.564308261950669</v>
+        <v>1.50666472837532</v>
       </c>
       <c r="F2021" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.3201131481671394</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.362193860352878</v>
+        <v>3.549353120185876</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>4.409480289874755</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.170151381698319</v>
+        <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.863964036576005</v>
       </c>
       <c r="E2022" t="n">
-        <v>3.564308261950669</v>
+        <v>1.3905568228782</v>
       </c>
       <c r="F2022" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.4097328824526236</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.362193860352878</v>
+        <v>3.490659132350775</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>4.409480289874755</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.170151381698319</v>
+        <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.980931729214896</v>
       </c>
       <c r="E2023" t="n">
-        <v>3.564308261950669</v>
+        <v>1.505973802521688</v>
       </c>
       <c r="F2023" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.4097328824526236</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.362193860352878</v>
+        <v>3.652863189049819</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>4.409480289874755</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.170151381698319</v>
+        <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>0.9862832614152426</v>
+        <v>-6.065649671435849</v>
       </c>
       <c r="E2024" t="n">
-        <v>3.564308261950669</v>
+        <v>1.466933263597121</v>
       </c>
       <c r="F2024" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.49484891138067</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.362193860352878</v>
+        <v>3.596640209656806</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>4.409480289874755</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.170151381698319</v>
+        <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>0.9862832614152426</v>
+        <v>-6.147584489704732</v>
       </c>
       <c r="E2025" t="n">
-        <v>3.564308261950669</v>
+        <v>1.444388753858058</v>
       </c>
       <c r="F2025" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.5047836569677502</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.362193860352878</v>
+        <v>3.600908779873049</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>4.409480289874755</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.170151381698319</v>
+        <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>0.9862832614152426</v>
+        <v>-6.249560611953139</v>
       </c>
       <c r="E2026" t="n">
-        <v>3.564308261950669</v>
+        <v>1.412523943414598</v>
       </c>
       <c r="F2026" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.6067597792161578</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.362193860352878</v>
+        <v>3.548648744979907</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>4.409480289874755</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.170151381698319</v>
+        <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>0.9862832614152426</v>
+        <v>-6.139554328475918</v>
       </c>
       <c r="E2027" t="n">
-        <v>3.564308261950669</v>
+        <v>1.448679344049662</v>
       </c>
       <c r="F2027" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.5835552072988826</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.362193860352878</v>
+        <v>3.554724375374447</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>4.409480289874755</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.170151381698319</v>
+        <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.996494752734993</v>
       </c>
       <c r="E2028" t="n">
-        <v>3.564308261950669</v>
+        <v>1.510153185068006</v>
       </c>
       <c r="F2028" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.5755417807089033</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.362193860352878</v>
+        <v>3.563782442050409</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>4.409480289874755</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.170151381698319</v>
+        <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.695048027263155</v>
       </c>
       <c r="E2029" t="n">
-        <v>3.564308261950669</v>
+        <v>1.637992758139277</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.274095055237066</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.362193860352878</v>
+        <v>3.751911360216047</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>4.409480289874755</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.170151381698319</v>
+        <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.719638271498339</v>
       </c>
       <c r="E2030" t="n">
-        <v>3.564308261950669</v>
+        <v>1.629127838197914</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.274095055237066</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.362193860352878</v>
+        <v>3.752882537968758</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>4.409480289874755</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.170151381698319</v>
+        <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.668599895491819</v>
       </c>
       <c r="E2031" t="n">
-        <v>3.564308261950669</v>
+        <v>1.650386092980277</v>
       </c>
       <c r="F2031" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.274095055237066</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.362193860352878</v>
+        <v>3.753725442348513</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>4.409480289874755</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.170151381698319</v>
+        <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.627460600625188</v>
       </c>
       <c r="E2032" t="n">
-        <v>3.564308261950669</v>
+        <v>1.685879909801075</v>
       </c>
       <c r="F2032" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.2329557603704352</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.362193860352878</v>
+        <v>3.797447118142637</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>4.409480289874755</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.170151381698319</v>
+        <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.516854460545586</v>
       </c>
       <c r="E2033" t="n">
-        <v>3.564308261950669</v>
+        <v>1.546306361956851</v>
       </c>
       <c r="F2033" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.1223496202908332</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.362193860352878</v>
+        <v>3.679994798314333</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>4.409480289874755</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.170151381698319</v>
+        <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.647435195076429</v>
       </c>
       <c r="E2034" t="n">
-        <v>3.564308261950669</v>
+        <v>1.497576112218477</v>
       </c>
       <c r="F2034" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.2529303548216757</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.362193860352878</v>
+        <v>3.605148401669791</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>4.409480289874755</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.170151381698319</v>
+        <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.482938860885467</v>
       </c>
       <c r="E2035" t="n">
-        <v>3.564308261950669</v>
+        <v>1.547801464970945</v>
       </c>
       <c r="F2035" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.2529303548216757</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.362193860352878</v>
+        <v>3.589575220745874</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>4.409480289874755</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.170151381698319</v>
+        <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.510308793569899</v>
       </c>
       <c r="E2036" t="n">
-        <v>3.564308261950669</v>
+        <v>1.536041202333601</v>
       </c>
       <c r="F2036" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.2529303548216757</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.362193860352878</v>
+        <v>3.588762931182303</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>4.409480289874755</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.170151381698319</v>
+        <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.520693988459788</v>
       </c>
       <c r="E2037" t="n">
-        <v>3.564308261950669</v>
+        <v>1.541755903502718</v>
       </c>
       <c r="F2037" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.263315549711565</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.362193860352878</v>
+        <v>3.592400593373442</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>4.409480289874755</v>
+        <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.170151381698319</v>
+        <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.539282147182013</v>
       </c>
       <c r="E2038" t="n">
-        <v>3.564308261950669</v>
+        <v>1.605157645790253</v>
       </c>
       <c r="F2038" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.2819037084337904</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.362193860352878</v>
+        <v>3.652084703916532</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>4.409480289874755</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.170151381698319</v>
+        <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.539580693878049</v>
       </c>
       <c r="E2039" t="n">
-        <v>3.564308261950669</v>
+        <v>1.601907237930138</v>
       </c>
       <c r="F2039" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.2819037084337904</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.362193860352878</v>
+        <v>3.648953714734831</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>4.409480289874755</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.170151381698319</v>
+        <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>0.9862832614152426</v>
+        <v>-5.438757560187621</v>
       </c>
       <c r="E2040" t="n">
-        <v>3.564308261950669</v>
+        <v>1.6467673863457</v>
       </c>
       <c r="F2040" t="n">
-        <v>1.986737464424265</v>
+        <v>-0.2694394929494365</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.362193860352878</v>
+        <v>3.660963138964834</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>4.396804193744029</v>
+        <v>3.807206190640606</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.170280635176862</v>
+        <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>0.967627403864443</v>
+        <v>-5.247976199435215</v>
       </c>
       <c r="E2041" t="n">
-        <v>3.556975172408892</v>
+        <v>1.723209184125206</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.985936726388033</v>
+        <v>-0.07865813219702916</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.361842671009683</v>
+        <v>3.775561208894822</v>
       </c>
     </row>
   </sheetData>
